--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,106 +425,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T23"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>County</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Case_or_TaxDeed_No</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Owner_Name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Entity_Type</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Is_Individual</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Heir_Search_Recommended</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Property_Address</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Property_Type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Surplus_Balance_USD</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Fee_Rate</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Est_Finder_Fee_USD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Opportunity_Tier</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Sale_Date</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Days_Remaining_To_Claim</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Claim_Urgency_Tier</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Claim_Deadline_Date</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Deadline_Window</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Clerk_Verification_URL</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Statute_Citation</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -582,31 +604,41 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -674,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -683,22 +715,32 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>2029-07-01</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -766,31 +808,41 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -858,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -867,22 +919,32 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>2029-08-12</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>https://www.cobbtax.org/</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -950,31 +1012,41 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1051,22 +1123,32 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>2029-07-15</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1134,31 +1216,41 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1226,31 +1318,41 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1364,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DeKalb</t>
+          <t>Dekalb</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1318,7 +1420,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1327,22 +1429,32 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>2029-08-05</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>https://www.dekalbcountytax.org/</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1410,31 +1522,41 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>https://www.dallascounty.org/</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1502,31 +1624,41 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1594,31 +1726,41 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1828,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1695,22 +1837,32 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
+          <t>2029-07-22</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>https://www.gwinnetttaxcommissioner.com/</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1778,31 +1930,41 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1870,31 +2032,41 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>https://www.dallascounty.org/</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1962,31 +2134,41 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -2054,31 +2236,41 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -2146,31 +2338,41 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -2238,31 +2440,41 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -2330,31 +2542,41 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -2422,31 +2644,41 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -2514,31 +2746,41 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:Y31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,100 +441,115 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Parcel_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Case_or_TaxDeed_No</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Owner_Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Entity_Type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Is_Individual</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Heir_Search_Recommended</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Property_Address</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Property_Type</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Surplus_Balance_USD</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Fee_Rate</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Est_Finder_Fee_USD</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Opportunity_Tier</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Sale_Date</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Days_Remaining_To_Claim</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Claim_Urgency_Tier</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Claim_Deadline_Date</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Deadline_Window</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Clerk_Verification_URL</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Statute_Citation</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Record_Type</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>TYPE</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -553,602 +568,692 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>50-43-43-15-06-001-0020</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>2024-TD-004501</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>ANTHONY &amp; GRACE VALENTINE</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F2" t="b">
+      <c r="G2" t="b">
         <v>1</v>
       </c>
-      <c r="G2" t="b">
+      <c r="H2" t="b">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>720 S OCEAN BLVD PALM BEACH FL 33480</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>145000</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>29000</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>2024-06-28</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>75</v>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fulton</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-GA-003810</t>
+          <t>4942-12-05-0890</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MARCUS &amp; ELEANOR JENKINS</t>
+          <t>2024-TD-003891</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>MARCUS &amp; HELENA VANDERBILT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F3" t="b">
+      <c r="G3" t="b">
         <v>1</v>
       </c>
-      <c r="G3" t="b">
+      <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1420 PEACHTREE ST NE ATLANTA GA 30309</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>1520 SE 12TH ST FORT LAUDERDALE FL 33316</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>134000</v>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="n">
+        <v>138500</v>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>26800</v>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="n">
+        <v>27700</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>1006</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
-        </is>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>75</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2029-07-01</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>O.C.G.A. § 48-4-5</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>O.C.G.A. § 48-4-5</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Fulton</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-TX-04812</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>WILLIAM &amp; MARY HOLLOWAY</t>
+          <t>2024-GA-003810</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>MARCUS &amp; ELEANOR JENKINS</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F4" t="b">
+      <c r="G4" t="b">
         <v>1</v>
       </c>
-      <c r="G4" t="b">
+      <c r="H4" t="b">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>5402 BRAESVALLEY DR HOUSTON TX 77096</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>1420 PEACHTREE ST NE ATLANTA GA 30309</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>128500</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>32125</v>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="K4" t="n">
+        <v>134000</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>26800</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>55</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
-        </is>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1005</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
+          <t>2029-07-01</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Tex. Tax Code § 34.04</t>
+          <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Tex. Tax Code § 34.04</t>
+          <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cobb</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-GA-001550</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ESTATE OF RAYMOND VAUGHN</t>
+          <t>2024-TX-04812</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Estate / Deceased</t>
-        </is>
-      </c>
-      <c r="F5" t="b">
-        <v>1</v>
+          <t>WILLIAM &amp; MARY HOLLOWAY</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1205 ROSWELL RD MARIETTA GA 30062</t>
-        </is>
+      <c r="H5" t="b">
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>5402 BRAESVALLEY DR HOUSTON TX 77096</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>118000</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>23600</v>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="K5" t="n">
+        <v>128500</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>32125</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>1048</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
-        </is>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>55</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2029-08-12</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://www.cobbtax.org/</t>
+          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>O.C.G.A. § 48-4-5</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>O.C.G.A. § 48-4-5</t>
+          <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Cobb</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-TD-004812</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LUIS &amp; MARIA HERNANDEZ</t>
+          <t>2024-GA-001550</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
-        </is>
-      </c>
-      <c r="F6" t="b">
+          <t>ESTATE OF RAYMOND VAUGHN</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
+      </c>
+      <c r="G6" t="b">
         <v>1</v>
       </c>
-      <c r="G6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>340 SW 8TH ST MIAMI FL 33130</t>
-        </is>
+      <c r="H6" t="b">
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>1205 ROSWELL RD MARIETTA GA 30062</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>112000</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="n">
+        <v>118000</v>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>22400</v>
-      </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="n">
+        <v>23600</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>75</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
-        </is>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1047</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+          <t>2029-08-12</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>https://www.cobbtax.org/</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fulton</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-GA-004120</t>
+          <t>02-3209-018-0240</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ESTATE OF HAROLD CRAWFORD</t>
+          <t>2024-CA-012874</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>ESTATE OF JULIAN MERCER</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Estate / Deceased</t>
         </is>
-      </c>
-      <c r="F7" t="b">
-        <v>1</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>892 CASCADE AVE SW ATLANTA GA 30310</t>
-        </is>
+      <c r="H7" t="b">
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>96500</v>
-      </c>
-      <c r="K7" t="inlineStr">
+          <t>1440 OCEAN DR APT 402 MIAMI BEACH FL 33139</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Condo / Multi-Family</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>115000</v>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>19300</v>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" t="n">
+        <v>23000</v>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>1020</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
-        </is>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>105</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2029-07-15</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>60 Days from Certificate of Disbursement (Fla. Stat. § 45.032)</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>O.C.G.A. § 48-4-5</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>O.C.G.A. § 48-4-5</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Foreclosure Surplus</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>FORECLOSURE</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -1160,505 +1265,580 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hillsborough</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-TD-008912</t>
+          <t>01-4138-005-0120</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ROBERT &amp; CLAIRE SULLIVAN</t>
+          <t>2024-TD-004812</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>LUIS &amp; MARIA HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F8" t="b">
+      <c r="G8" t="b">
         <v>1</v>
       </c>
-      <c r="G8" t="b">
+      <c r="H8" t="b">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>4502 W SAN RAFAEL ST TAMPA FL 33629</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>340 SW 8TH ST MIAMI FL 33130</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>92400</v>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="n">
+        <v>112000</v>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>18480</v>
-      </c>
-      <c r="M8" t="inlineStr">
+      <c r="M8" t="n">
+        <v>22400</v>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
         <v>75</v>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R8" t="inlineStr">
         <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>https://www.hillsclerk.com/</t>
-        </is>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
+          <t>https://www.miamidadeclerk.gov/</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Fulton</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-TX-04950</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ESTATE OF CHARLES BEAUMONT</t>
+          <t>2024-GA-004120</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>ESTATE OF HAROLD CRAWFORD</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Estate / Deceased</t>
         </is>
-      </c>
-      <c r="F9" t="b">
-        <v>1</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1802 HEIGHTS BLVD HOUSTON TX 77008</t>
-        </is>
+      <c r="H9" t="b">
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>892 CASCADE AVE SW ATLANTA GA 30310</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>86200</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>21550</v>
-      </c>
-      <c r="M9" t="inlineStr">
+      <c r="K9" t="n">
+        <v>96500</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>19300</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="O9" t="n">
-        <v>55</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
-        </is>
+      <c r="P9" t="n">
+        <v>1019</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
+          <t>2029-07-15</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Tex. Tax Code § 34.04</t>
+          <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Tex. Tax Code § 34.04</t>
+          <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dekalb</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-GA-002490</t>
+          <t>182914-4TA000001000020</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>TERRENCE &amp; MONICA BRADLEY</t>
+          <t>2024-TD-008912</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>ROBERT &amp; CLAIRE SULLIVAN</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F10" t="b">
+      <c r="G10" t="b">
         <v>1</v>
       </c>
-      <c r="G10" t="b">
+      <c r="H10" t="b">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2340 LAVISTA RD DECATUR GA 30033</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>4502 W SAN RAFAEL ST TAMPA FL 33629</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>82400</v>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="n">
+        <v>92400</v>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L10" t="n">
-        <v>16480</v>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="M10" t="n">
+        <v>18480</v>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>1041</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
-        </is>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>75</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2029-08-05</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.dekalbcountytax.org/</t>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>O.C.G.A. § 48-4-5</t>
+          <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>O.C.G.A. § 48-4-5</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-TX-02044</t>
+          <t>30-4014-012-0580</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ESTATE OF MARGARET THORNTON</t>
+          <t>2024-CA-014289</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>ESTATE OF VICTORIA CRANE</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>Estate / Deceased</t>
         </is>
-      </c>
-      <c r="F11" t="b">
-        <v>1</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>6412 ABRAMS RD DALLAS TX 75231</t>
-        </is>
+      <c r="H11" t="b">
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>10845 SW 72ND AVE MIAMI FL 33156</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>77800</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>19450</v>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="K11" t="n">
+        <v>89450</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>17890</v>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>55</v>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>60 Days from Certificate of Disbursement (Fla. Stat. § 45.032)</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Tex. Tax Code § 34.04</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Tex. Tax Code § 34.04</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Foreclosure Surplus</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>FORECLOSURE</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-TD-001955</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>JAMES &amp; LINDA CHEN</t>
+          <t>2024-TX-04950</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
-        </is>
-      </c>
-      <c r="F12" t="b">
+          <t>ESTATE OF CHARLES BEAUMONT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
         <v>1</v>
       </c>
-      <c r="G12" t="b">
-        <v>0</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>8431 BAY BREEZE WAY ORLANDO FL 32836</t>
-        </is>
+      <c r="H12" t="b">
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>1802 HEIGHTS BLVD HOUSTON TX 77008</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>74300</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>14860</v>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="K12" t="n">
+        <v>86200</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>21550</v>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2024-08-08</t>
-        </is>
-      </c>
-      <c r="O12" t="n">
-        <v>75</v>
-      </c>
-      <c r="P12" t="inlineStr">
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -1670,97 +1850,112 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Palm Beach</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-TD-004688</t>
+          <t>5142-28-03-0140</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ESTATE OF ARTHUR STERLING</t>
+          <t>2024-TD-004105</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>ESTATE OF RAYMOND CHANDLER</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>Estate / Deceased</t>
         </is>
-      </c>
-      <c r="F13" t="b">
-        <v>1</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>1410 N FEDERAL HWY LAKE WORTH FL 33460</t>
-        </is>
+      <c r="H13" t="b">
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>3840 N 56TH AVE HOLLYWOOD FL 33021</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>68900</v>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" t="n">
+        <v>84200</v>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L13" t="n">
-        <v>13780</v>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="M13" t="n">
+        <v>16840</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="O13" t="n">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
         <v>75</v>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R13" t="inlineStr">
         <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
-        </is>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
+          <t>https://www.browardclerk.org/</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -1772,97 +1967,112 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gwinnett</t>
+          <t>Dekalb</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-GA-001920</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VICTORIA STRICKLAND</t>
+          <t>2024-GA-002490</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>TERRENCE &amp; MONICA BRADLEY</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F14" t="b">
+      <c r="G14" t="b">
         <v>1</v>
       </c>
-      <c r="G14" t="b">
+      <c r="H14" t="b">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>4510 LAWRENCEVILLE HWY LILBURN GA 30047</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>2340 LAVISTA RD DECATUR GA 30033</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>67800</v>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" t="n">
+        <v>82400</v>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L14" t="n">
-        <v>13560</v>
-      </c>
-      <c r="M14" t="inlineStr">
+      <c r="M14" t="n">
+        <v>16480</v>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="O14" t="n">
-        <v>1027</v>
-      </c>
-      <c r="P14" t="inlineStr">
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1040</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>2029-07-22</t>
-        </is>
-      </c>
       <c r="R14" t="inlineStr">
         <is>
+          <t>2029-08-05</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>https://www.gwinnetttaxcommissioner.com/</t>
-        </is>
-      </c>
       <c r="T14" t="inlineStr">
         <is>
+          <t>https://www.dekalbcountytax.org/</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -1874,97 +2084,112 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Palm Beach</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-TD-001501</t>
+          <t>00-43-43-05-11-002-0080</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ESTATE OF ELEANOR VANCE</t>
+          <t>2024-CA-006731</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Estate / Deceased</t>
-        </is>
-      </c>
-      <c r="F15" t="b">
-        <v>1</v>
+          <t>REBECCA &amp; GERALD MONROE</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
       </c>
       <c r="G15" t="b">
         <v>1</v>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>3309 ROSEWOOD CT WINTER PARK FL 32792</t>
-        </is>
+      <c r="H15" t="b">
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>318 COLONIAL RD WEST PALM BEACH FL 33405</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>61800</v>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" t="n">
+        <v>78250</v>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L15" t="n">
-        <v>12360</v>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="M15" t="n">
+        <v>15650</v>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2024-07-03</t>
-        </is>
-      </c>
-      <c r="O15" t="n">
-        <v>75</v>
-      </c>
-      <c r="P15" t="inlineStr">
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>60 Days from Certificate of Disbursement (Fla. Stat. § 45.032)</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Foreclosure Surplus</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>FORECLOSURE</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -1981,92 +2206,107 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-TX-01928</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>GEORGE &amp; DOROTHY WASHINGTON</t>
+          <t>2024-TX-02044</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
-        </is>
-      </c>
-      <c r="F16" t="b">
+          <t>ESTATE OF MARGARET THORNTON</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
         <v>1</v>
       </c>
-      <c r="G16" t="b">
-        <v>0</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>3819 COLONIAL AVE DALLAS TX 75215</t>
-        </is>
+      <c r="H16" t="b">
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t>6412 ABRAMS RD DALLAS TX 75231</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J16" t="n">
-        <v>59400</v>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" t="n">
+        <v>77800</v>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="L16" t="n">
-        <v>14850</v>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="M16" t="n">
+        <v>19450</v>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="O16" t="n">
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
         <v>55</v>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
       <c r="R16" t="inlineStr">
         <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>https://www.dallascounty.org/</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -2078,97 +2318,112 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hillsborough</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-TD-009041</t>
+          <t>28-23-27-0000-00-015</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ESTATE OF HENRY PATTERSON</t>
+          <t>2024-TD-001955</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Estate / Deceased</t>
-        </is>
-      </c>
-      <c r="F17" t="b">
-        <v>1</v>
+          <t>JAMES &amp; LINDA CHEN</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
       </c>
       <c r="G17" t="b">
         <v>1</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>11804 N 56TH ST TEMPLE TERRACE FL 33617</t>
-        </is>
+      <c r="H17" t="b">
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>8431 BAY BREEZE WAY ORLANDO FL 32836</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>54100</v>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" t="n">
+        <v>74300</v>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L17" t="n">
-        <v>10820</v>
-      </c>
-      <c r="M17" t="inlineStr">
+      <c r="M17" t="n">
+        <v>14860</v>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="O17" t="n">
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
         <v>75</v>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R17" t="inlineStr">
         <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>https://www.hillsclerk.com/</t>
-        </is>
-      </c>
       <c r="T17" t="inlineStr">
         <is>
+          <t>https://www.myorangeclerk.com/</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -2180,301 +2435,346 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Palm Beach</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-TD-001248</t>
+          <t>00-42-43-27-05-022-0140</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>RICHARD HAWKINS</t>
+          <t>2024-TD-004688</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
-        </is>
-      </c>
-      <c r="F18" t="b">
+          <t>ESTATE OF ARTHUR STERLING</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
         <v>1</v>
       </c>
-      <c r="G18" t="b">
-        <v>0</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>1420 PINEWOOD DR ORLANDO FL 32808</t>
-        </is>
+      <c r="H18" t="b">
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>1410 N FEDERAL HWY LAKE WORTH FL 33460</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J18" t="n">
-        <v>48250</v>
-      </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" t="n">
+        <v>68900</v>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L18" t="n">
-        <v>9650</v>
-      </c>
-      <c r="M18" t="inlineStr">
+      <c r="M18" t="n">
+        <v>13780</v>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="O18" t="n">
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
         <v>75</v>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R18" t="inlineStr">
         <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>https://www.myorangeclerk.com/</t>
-        </is>
-      </c>
       <c r="T18" t="inlineStr">
         <is>
+          <t>https://www.mypalmbeachclerk.com/</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Gwinnett</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-TD-004990</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EUGENE FITZPATRICK</t>
+          <t>2024-GA-001920</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>VICTORIA STRICKLAND</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F19" t="b">
+      <c r="G19" t="b">
         <v>1</v>
       </c>
-      <c r="G19" t="b">
+      <c r="H19" t="b">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>1920 CORAL WAY MIAMI FL 33145</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>4510 LAWRENCEVILLE HWY LILBURN GA 30047</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J19" t="n">
-        <v>43500</v>
-      </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" t="n">
+        <v>67800</v>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L19" t="n">
-        <v>8700</v>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="M19" t="n">
+        <v>13560</v>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="O19" t="n">
-        <v>75</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
-        </is>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1026</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+          <t>2029-07-22</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>https://www.gwinnetttaxcommissioner.com/</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-TX-05110</t>
+          <t>4842-18-09-0410</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>RAFAEL GUERRERO</t>
+          <t>2024-CA-009842</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
-        </is>
-      </c>
-      <c r="F20" t="b">
+          <t>ESTATE OF LAWRENCE THORNE</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
         <v>1</v>
       </c>
-      <c r="G20" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>7120 NAVIGATION BLVD HOUSTON TX 77011</t>
-        </is>
+      <c r="H20" t="b">
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t>4210 NE 22ND AVE LIGHTHOUSE POINT FL 33064</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J20" t="n">
-        <v>41300</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>10325</v>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="K20" t="n">
+        <v>64800</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>12960</v>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="O20" t="n">
-        <v>55</v>
-      </c>
-      <c r="P20" t="inlineStr">
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>60 Days from Certificate of Disbursement (Fla. Stat. § 45.032)</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>Tex. Tax Code § 34.04</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Tex. Tax Code § 34.04</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Foreclosure Surplus</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>FORECLOSURE</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -2486,199 +2786,229 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hillsborough</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-TD-009188</t>
+          <t>29-22-30-0000-00-042</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DANIELLE KAUFMAN</t>
+          <t>2024-TD-001501</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
-        </is>
-      </c>
-      <c r="F21" t="b">
+          <t>ESTATE OF ELEANOR VANCE</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
+      </c>
+      <c r="G21" t="b">
         <v>1</v>
       </c>
-      <c r="G21" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2308 S ARMENIA AVE TAMPA FL 33629</t>
-        </is>
+      <c r="H21" t="b">
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>3309 ROSEWOOD CT WINTER PARK FL 32792</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J21" t="n">
-        <v>31750</v>
-      </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" t="n">
+        <v>61800</v>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L21" t="n">
-        <v>6350</v>
-      </c>
-      <c r="M21" t="inlineStr">
+      <c r="M21" t="n">
+        <v>12360</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2024-08-10</t>
-        </is>
-      </c>
-      <c r="O21" t="n">
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
         <v>75</v>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R21" t="inlineStr">
         <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>https://www.hillsclerk.com/</t>
-        </is>
-      </c>
       <c r="T21" t="inlineStr">
         <is>
+          <t>https://www.myorangeclerk.com/</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-TD-001622</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MARCOS &amp; SOFIA ALVAREZ</t>
+          <t>2024-TX-01928</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>GEORGE &amp; DOROTHY WASHINGTON</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F22" t="b">
+      <c r="G22" t="b">
         <v>1</v>
       </c>
-      <c r="G22" t="b">
+      <c r="H22" t="b">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>510 LAKE BREEZE DR APOPKA FL 32703</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t>3819 COLONIAL AVE DALLAS TX 75215</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J22" t="n">
-        <v>29400</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>5880</v>
-      </c>
-      <c r="M22" t="inlineStr">
+      <c r="K22" t="n">
+        <v>59400</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>14850</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2024-07-17</t>
-        </is>
-      </c>
-      <c r="O22" t="n">
-        <v>75</v>
-      </c>
-      <c r="P22" t="inlineStr">
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>https://www.dallascounty.org/</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -2690,97 +3020,1048 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>Hillsborough</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>192802-5TB000002000040</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2024-TD-009041</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ESTATE OF HENRY PATTERSON</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
+      </c>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>11804 N 56TH ST TEMPLE TERRACE FL 33617</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>54100</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>10820</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>https://www.hillsclerk.com/</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Broward</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>4842-35-08-0320</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2024-TD-002980</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PATRICIA &amp; GLENN O'CONNOR</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2100 NE 48TH ST POMPANO BEACH FL 33064</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>52700</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>10540</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>https://www.browardclerk.org/</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>Orange</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>29-22-29-0000-00-088</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2024-TD-001248</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RICHARD HAWKINS</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1420 PINEWOOD DR ORLANDO FL 32808</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>48250</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>9650</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>https://www.myorangeclerk.com/</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Miami-Dade</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>01-3122-015-0450</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2024-TD-004990</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>EUGENE FITZPATRICK</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G26" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1920 CORAL WAY MIAMI FL 33145</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>43500</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>8700</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>https://www.miamidadeclerk.gov/</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Broward</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>5041-35-02-0190</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2024-CA-011205</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>THOMAS &amp; CLARA WHITFIELD</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8920 SW 18TH ST PLANTATION FL 33324</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>41600</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>8320</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2027-01-13</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>60 Days from Certificate of Disbursement (Fla. Stat. § 45.032)</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>https://www.browardclerk.org/</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Foreclosure Surplus</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>FORECLOSURE</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2024-TX-05110</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAFAEL GUERRERO</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>7120 NAVIGATION BLVD HOUSTON TX 77011</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>41300</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>10325</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>https://www.hcdistrictclerk.com/</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Hillsborough</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>182923-3TC000001000010</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2024-TD-009188</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>DANIELLE KAUFMAN</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2308 S ARMENIA AVE TAMPA FL 33629</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>31750</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>6350</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2024-08-10</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>https://www.hillsclerk.com/</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>28-21-15-0000-00-031</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2024-TD-001622</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>MARCOS &amp; SOFIA ALVAREZ</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G30" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>510 LAKE BREEZE DR APOPKA FL 32703</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>29400</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>5880</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>https://www.myorangeclerk.com/</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>29-23-35-0000-00-019</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>2024-TD-001844</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>BEATRICE MONTGOMERY</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F23" t="b">
+      <c r="G31" t="b">
         <v>1</v>
       </c>
-      <c r="G23" t="b">
+      <c r="H31" t="b">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>220 W KALEY ST ORLANDO FL 32806</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="K31" t="n">
         <v>18900</v>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="M31" t="n">
         <v>3780</v>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Tier 2: Medium Value ($10k-$25k)</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>2024-08-01</t>
         </is>
       </c>
-      <c r="O23" t="n">
+      <c r="P31" t="n">
         <v>75</v>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
         <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-17</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-17</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-17</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-17</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-17</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004501</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-003891</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>https://www.fultonclerk.org/case-search?docket=2024-GA-003810</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04812</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.cobbtax.org/</t>
+          <t>https://www.cobbtax.org/excess-funds?docket=2024-GA-001550</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www2.miamidadeclerk.gov/ocs/Search.aspx?caseNumber=2024-CA-012874</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www.miamidadeclerk.gov/clerk/tax-deeds.page?caseNumber=2024-TD-004812</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>https://www.fultonclerk.org/case-search?docket=2024-GA-004120</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-008912</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www2.miamidadeclerk.gov/ocs/Search.aspx?caseNumber=2024-CA-014289</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04950</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-004105</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>https://www.dekalbcountytax.org/</t>
+          <t>https://www.dekalbcountytax.org/excess-funds?docket=2024-GA-002490</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-CA-006731</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>https://www.dallascounty.org/government/district-clerk/tax-foreclosures.php?case=2024-TX-02044</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001955</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004688</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>https://www.gwinnetttaxcommissioner.com/</t>
+          <t>https://www.gwinnetttaxcommissioner.com/excess-funds?docket=2024-GA-001920</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-009842</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001501</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>https://www.dallascounty.org/government/district-clerk/tax-foreclosures.php?case=2024-TX-01928</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-009041</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-002980</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001248</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www.miamidadeclerk.gov/clerk/tax-deeds.page?caseNumber=2024-TD-004990</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-011205</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-05110</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-009188</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001622</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001844</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004501</t>
+          <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-003891</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/case-search?docket=2024-GA-003810</t>
+          <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04812</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.cobbtax.org/excess-funds?docket=2024-GA-001550</t>
+          <t>https://www.cobbtax.org/</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://www2.miamidadeclerk.gov/ocs/Search.aspx?caseNumber=2024-CA-012874</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/clerk/tax-deeds.page?caseNumber=2024-TD-004812</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/case-search?docket=2024-GA-004120</t>
+          <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-008912</t>
+          <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://www2.miamidadeclerk.gov/ocs/Search.aspx?caseNumber=2024-CA-014289</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04950</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-004105</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>https://www.dekalbcountytax.org/excess-funds?docket=2024-GA-002490</t>
+          <t>https://www.dekalbcountytax.org/</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-CA-006731</t>
+          <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/government/district-clerk/tax-foreclosures.php?case=2024-TX-02044</t>
+          <t>https://www.dallascounty.org/</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001955</t>
+          <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004688</t>
+          <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>https://www.gwinnetttaxcommissioner.com/excess-funds?docket=2024-GA-001920</t>
+          <t>https://www.gwinnetttaxcommissioner.com/</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-009842</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001501</t>
+          <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/government/district-clerk/tax-foreclosures.php?case=2024-TX-01928</t>
+          <t>https://www.dallascounty.org/</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-009041</t>
+          <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-002980</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001248</t>
+          <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/clerk/tax-deeds.page?caseNumber=2024-TD-004990</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-011205</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-05110</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-009188</t>
+          <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001622</t>
+          <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001844</t>
+          <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://www.mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004501</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-003891</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>https://www.fultonclerk.org/536/Records-Search-Center?docket=2024-GA-003810</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04812</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.cobbtax.org/</t>
+          <t>https://www.cobbtax.org/property/tax_sale/index.php?docket=2024-GA-001550</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www2.miamidadeclerk.gov/QOS/default.aspx?caseNumber=2024-CA-012874</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www.miamidadeclerk.gov/clerk/property-tax-deeds.page?caseNumber=2024-TD-004812</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>https://www.fultonclerk.org/536/Records-Search-Center?docket=2024-GA-004120</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/taxdeeds?caseNumber=2024-TD-008912</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www2.miamidadeclerk.gov/QOS/default.aspx?caseNumber=2024-CA-014289</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04950</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-004105</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>https://www.dekalbcountytax.org/</t>
+          <t>https://www.dekalbcountytax.org/excess-funds?docket=2024-GA-002490</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://www.mypalmbeachclerk.com/casesearch?caseNumber=2024-CA-006731</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>https://www.dallascounty.org/government/county-clerk/recording/foreclosures.php?case=2024-TX-02044</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myeclerk.myorangeclerk.com/?caseNumber=2024-TD-001955</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://www.mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004688</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>https://www.gwinnetttaxcommissioner.com/</t>
+          <t>https://www.gwinnetttaxcommissioner.com/property-tax/tax-sale-excess-funds?docket=2024-GA-001920</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-009842</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myeclerk.myorangeclerk.com/?caseNumber=2024-TD-001501</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>https://www.dallascounty.org/government/county-clerk/recording/foreclosures.php?case=2024-TX-01928</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/taxdeeds?caseNumber=2024-TD-009041</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-002980</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myeclerk.myorangeclerk.com/?caseNumber=2024-TD-001248</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www.miamidadeclerk.gov/clerk/property-tax-deeds.page?caseNumber=2024-TD-004990</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-011205</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-05110</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/taxdeeds?caseNumber=2024-TD-009188</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myeclerk.myorangeclerk.com/?caseNumber=2024-TD-001622</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myeclerk.myorangeclerk.com/?caseNumber=2024-TD-001844</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7592,7 +7592,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8238,7 +8238,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8620,7 +8620,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9390,7 +9390,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9640,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9890,7 +9890,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10518,7 +10518,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10890,7 +10890,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11278,7 +11278,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11534,7 +11534,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11912,7 +11912,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12162,7 +12162,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12284,7 +12284,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12416,7 +12416,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12548,7 +12548,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12680,7 +12680,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12802,7 +12802,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13180,7 +13180,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13308,7 +13308,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13436,7 +13436,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13564,7 +13564,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13692,7 +13692,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13948,7 +13948,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14080,7 +14080,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14202,7 +14202,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14330,7 +14330,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14452,7 +14452,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14580,7 +14580,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14840,7 +14840,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14968,7 +14968,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15096,7 +15096,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15218,7 +15218,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15350,7 +15350,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15478,7 +15478,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15862,7 +15862,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15990,7 +15990,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16250,7 +16250,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16382,7 +16382,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16510,7 +16510,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16638,7 +16638,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16770,7 +16770,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16892,7 +16892,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17020,7 +17020,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17142,7 +17142,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17392,7 +17392,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17514,7 +17514,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17642,7 +17642,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17764,7 +17764,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18024,7 +18024,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18152,7 +18152,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18274,7 +18274,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18402,7 +18402,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18530,7 +18530,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18658,7 +18658,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18790,7 +18790,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18918,7 +18918,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19296,7 +19296,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19424,7 +19424,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19546,7 +19546,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19674,7 +19674,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19796,7 +19796,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19918,7 +19918,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20046,7 +20046,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20178,7 +20178,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20310,7 +20310,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20570,7 +20570,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20698,7 +20698,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20830,7 +20830,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20952,7 +20952,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21080,7 +21080,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21208,7 +21208,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21336,7 +21336,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21468,7 +21468,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21724,7 +21724,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21846,7 +21846,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21974,7 +21974,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22102,7 +22102,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22234,7 +22234,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22356,7 +22356,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22484,7 +22484,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22606,7 +22606,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22734,7 +22734,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22866,7 +22866,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22988,7 +22988,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -23116,7 +23116,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -23244,7 +23244,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -23372,7 +23372,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -23500,7 +23500,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -23628,7 +23628,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -23756,7 +23756,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -23884,7 +23884,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -24006,7 +24006,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -24134,7 +24134,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -24256,7 +24256,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -24384,7 +24384,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -24512,7 +24512,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -24634,7 +24634,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -24762,7 +24762,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -24890,7 +24890,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -25150,7 +25150,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -25278,7 +25278,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -25406,7 +25406,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -25534,7 +25534,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -25662,7 +25662,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -25784,7 +25784,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -25912,7 +25912,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -26044,7 +26044,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -26176,7 +26176,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -26304,7 +26304,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -26426,7 +26426,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -26548,7 +26548,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -26670,7 +26670,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -26798,7 +26798,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -27182,7 +27182,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -27436,7 +27436,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -27568,7 +27568,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -27700,7 +27700,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -27832,7 +27832,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -27960,7 +27960,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -28088,7 +28088,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -28216,7 +28216,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -28344,7 +28344,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -28472,7 +28472,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -28604,7 +28604,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -28726,7 +28726,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -28854,7 +28854,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -28986,7 +28986,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -29114,7 +29114,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -29242,7 +29242,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -29486,7 +29486,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -29614,7 +29614,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -29742,7 +29742,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -29992,7 +29992,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -30120,7 +30120,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -30248,7 +30248,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -30370,7 +30370,7 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -30492,7 +30492,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -30614,7 +30614,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -30736,7 +30736,7 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -30858,7 +30858,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -30986,7 +30986,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -31246,7 +31246,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -31378,7 +31378,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -31510,7 +31510,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -31632,7 +31632,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -31754,7 +31754,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -31882,7 +31882,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -32014,7 +32014,7 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -32142,7 +32142,7 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -32274,7 +32274,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -32402,7 +32402,7 @@
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -32530,7 +32530,7 @@
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -32652,7 +32652,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -32780,7 +32780,7 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -32912,7 +32912,7 @@
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -33034,7 +33034,7 @@
       </c>
       <c r="AB256" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -33156,7 +33156,7 @@
       </c>
       <c r="AB257" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -33284,7 +33284,7 @@
       </c>
       <c r="AB258" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -33406,7 +33406,7 @@
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -33538,7 +33538,7 @@
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -33670,7 +33670,7 @@
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -33792,7 +33792,7 @@
       </c>
       <c r="AB262" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -33914,7 +33914,7 @@
       </c>
       <c r="AB263" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="AB264" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -34178,7 +34178,7 @@
       </c>
       <c r="AB265" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -34310,7 +34310,7 @@
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -34442,7 +34442,7 @@
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -34564,7 +34564,7 @@
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -34692,7 +34692,7 @@
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -34820,7 +34820,7 @@
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -34942,7 +34942,7 @@
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -35070,7 +35070,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -35198,7 +35198,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -35326,7 +35326,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -35454,7 +35454,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -35586,7 +35586,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -35708,7 +35708,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -35836,7 +35836,7 @@
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -35968,7 +35968,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -36096,7 +36096,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -36346,7 +36346,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -36468,7 +36468,7 @@
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -36596,7 +36596,7 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -36728,7 +36728,7 @@
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -36856,7 +36856,7 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -36988,7 +36988,7 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -37120,7 +37120,7 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -37252,7 +37252,7 @@
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -37384,7 +37384,7 @@
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -37516,7 +37516,7 @@
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -37772,7 +37772,7 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -37894,7 +37894,7 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -38016,7 +38016,7 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -38138,7 +38138,7 @@
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -38270,7 +38270,7 @@
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -38402,7 +38402,7 @@
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -38530,7 +38530,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -38652,7 +38652,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -38780,7 +38780,7 @@
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -38902,7 +38902,7 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -39024,7 +39024,7 @@
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -39146,7 +39146,7 @@
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -39278,7 +39278,7 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -39400,7 +39400,7 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -39532,7 +39532,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -39654,7 +39654,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -39776,7 +39776,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -39904,7 +39904,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -40032,7 +40032,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -40164,7 +40164,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -40286,7 +40286,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -40408,7 +40408,7 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -40540,7 +40540,7 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -40672,7 +40672,7 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -40800,7 +40800,7 @@
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -40928,7 +40928,7 @@
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -41050,7 +41050,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -41182,7 +41182,7 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -41304,7 +41304,7 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -41432,7 +41432,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -41554,7 +41554,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -41676,7 +41676,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -41808,7 +41808,7 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -41940,7 +41940,7 @@
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -42062,7 +42062,7 @@
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -42194,7 +42194,7 @@
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -42322,7 +42322,7 @@
       </c>
       <c r="AB329" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -42444,7 +42444,7 @@
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -42566,7 +42566,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -42698,7 +42698,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -42830,7 +42830,7 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -42958,7 +42958,7 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -43090,7 +43090,7 @@
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -43218,7 +43218,7 @@
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -43350,7 +43350,7 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -43472,7 +43472,7 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -43594,7 +43594,7 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -43716,7 +43716,7 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -43848,7 +43848,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -43970,7 +43970,7 @@
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -44102,7 +44102,7 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -44224,7 +44224,7 @@
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -44352,7 +44352,7 @@
       </c>
       <c r="AB345" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -44484,7 +44484,7 @@
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -44606,7 +44606,7 @@
       </c>
       <c r="AB347" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -44728,7 +44728,7 @@
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -44860,7 +44860,7 @@
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -44988,7 +44988,7 @@
       </c>
       <c r="AB350" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -45110,7 +45110,7 @@
       </c>
       <c r="AB351" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -45232,7 +45232,7 @@
       </c>
       <c r="AB352" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -45354,7 +45354,7 @@
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -45476,7 +45476,7 @@
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -45608,7 +45608,7 @@
       </c>
       <c r="AB355" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -45736,7 +45736,7 @@
       </c>
       <c r="AB356" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -45868,7 +45868,7 @@
       </c>
       <c r="AB357" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -45990,7 +45990,7 @@
       </c>
       <c r="AB358" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -46122,7 +46122,7 @@
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -46254,7 +46254,7 @@
       </c>
       <c r="AB360" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -46376,7 +46376,7 @@
       </c>
       <c r="AB361" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -46504,7 +46504,7 @@
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -46632,7 +46632,7 @@
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -46760,7 +46760,7 @@
       </c>
       <c r="AB364" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -46882,7 +46882,7 @@
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -47010,7 +47010,7 @@
       </c>
       <c r="AB366" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -47132,7 +47132,7 @@
       </c>
       <c r="AB367" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -47260,7 +47260,7 @@
       </c>
       <c r="AB368" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -47382,7 +47382,7 @@
       </c>
       <c r="AB369" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -47514,7 +47514,7 @@
       </c>
       <c r="AB370" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -47636,7 +47636,7 @@
       </c>
       <c r="AB371" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -47764,7 +47764,7 @@
       </c>
       <c r="AB372" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -47896,7 +47896,7 @@
       </c>
       <c r="AB373" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -48028,7 +48028,7 @@
       </c>
       <c r="AB374" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -48156,7 +48156,7 @@
       </c>
       <c r="AB375" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -48288,7 +48288,7 @@
       </c>
       <c r="AB376" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -48420,7 +48420,7 @@
       </c>
       <c r="AB377" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -48548,7 +48548,7 @@
       </c>
       <c r="AB378" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -48670,7 +48670,7 @@
       </c>
       <c r="AB379" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -48792,7 +48792,7 @@
       </c>
       <c r="AB380" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -48924,7 +48924,7 @@
       </c>
       <c r="AB381" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -49056,7 +49056,7 @@
       </c>
       <c r="AB382" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -49188,7 +49188,7 @@
       </c>
       <c r="AB383" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -49310,7 +49310,7 @@
       </c>
       <c r="AB384" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -49442,7 +49442,7 @@
       </c>
       <c r="AB385" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -49570,7 +49570,7 @@
       </c>
       <c r="AB386" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -49702,7 +49702,7 @@
       </c>
       <c r="AB387" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -49824,7 +49824,7 @@
       </c>
       <c r="AB388" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -49956,7 +49956,7 @@
       </c>
       <c r="AB389" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -50084,7 +50084,7 @@
       </c>
       <c r="AB390" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -50206,7 +50206,7 @@
       </c>
       <c r="AB391" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -50334,7 +50334,7 @@
       </c>
       <c r="AB392" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -50456,7 +50456,7 @@
       </c>
       <c r="AB393" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -50584,7 +50584,7 @@
       </c>
       <c r="AB394" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -50712,7 +50712,7 @@
       </c>
       <c r="AB395" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -50834,7 +50834,7 @@
       </c>
       <c r="AB396" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -50956,7 +50956,7 @@
       </c>
       <c r="AB397" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -51078,7 +51078,7 @@
       </c>
       <c r="AB398" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -51200,7 +51200,7 @@
       </c>
       <c r="AB399" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -51322,7 +51322,7 @@
       </c>
       <c r="AB400" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -51444,7 +51444,7 @@
       </c>
       <c r="AB401" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -51572,7 +51572,7 @@
       </c>
       <c r="AB402" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -51700,7 +51700,7 @@
       </c>
       <c r="AB403" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -51832,7 +51832,7 @@
       </c>
       <c r="AB404" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -51964,7 +51964,7 @@
       </c>
       <c r="AB405" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -52086,7 +52086,7 @@
       </c>
       <c r="AB406" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -52208,7 +52208,7 @@
       </c>
       <c r="AB407" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -52340,7 +52340,7 @@
       </c>
       <c r="AB408" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -52472,7 +52472,7 @@
       </c>
       <c r="AB409" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -52594,7 +52594,7 @@
       </c>
       <c r="AB410" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -52722,7 +52722,7 @@
       </c>
       <c r="AB411" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -52854,7 +52854,7 @@
       </c>
       <c r="AB412" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -52986,7 +52986,7 @@
       </c>
       <c r="AB413" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -53108,7 +53108,7 @@
       </c>
       <c r="AB414" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -53236,7 +53236,7 @@
       </c>
       <c r="AB415" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -53368,7 +53368,7 @@
       </c>
       <c r="AB416" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -53500,7 +53500,7 @@
       </c>
       <c r="AB417" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -53632,7 +53632,7 @@
       </c>
       <c r="AB418" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -53754,7 +53754,7 @@
       </c>
       <c r="AB419" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -53886,7 +53886,7 @@
       </c>
       <c r="AB420" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -54008,7 +54008,7 @@
       </c>
       <c r="AB421" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -54130,7 +54130,7 @@
       </c>
       <c r="AB422" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -54252,7 +54252,7 @@
       </c>
       <c r="AB423" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -54374,7 +54374,7 @@
       </c>
       <c r="AB424" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -54496,7 +54496,7 @@
       </c>
       <c r="AB425" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -54628,7 +54628,7 @@
       </c>
       <c r="AB426" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -54760,7 +54760,7 @@
       </c>
       <c r="AB427" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -54882,7 +54882,7 @@
       </c>
       <c r="AB428" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -55004,7 +55004,7 @@
       </c>
       <c r="AB429" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -55126,7 +55126,7 @@
       </c>
       <c r="AB430" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -55248,7 +55248,7 @@
       </c>
       <c r="AB431" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -55380,7 +55380,7 @@
       </c>
       <c r="AB432" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -55512,7 +55512,7 @@
       </c>
       <c r="AB433" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -55644,7 +55644,7 @@
       </c>
       <c r="AB434" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -55766,7 +55766,7 @@
       </c>
       <c r="AB435" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -55888,7 +55888,7 @@
       </c>
       <c r="AB436" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -56020,7 +56020,7 @@
       </c>
       <c r="AB437" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -56152,7 +56152,7 @@
       </c>
       <c r="AB438" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -56274,7 +56274,7 @@
       </c>
       <c r="AB439" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -56406,7 +56406,7 @@
       </c>
       <c r="AB440" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -56528,7 +56528,7 @@
       </c>
       <c r="AB441" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -56650,7 +56650,7 @@
       </c>
       <c r="AB442" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -56778,7 +56778,7 @@
       </c>
       <c r="AB443" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -56900,7 +56900,7 @@
       </c>
       <c r="AB444" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -57022,7 +57022,7 @@
       </c>
       <c r="AB445" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -57154,7 +57154,7 @@
       </c>
       <c r="AB446" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -57276,7 +57276,7 @@
       </c>
       <c r="AB447" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -57398,7 +57398,7 @@
       </c>
       <c r="AB448" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -57520,7 +57520,7 @@
       </c>
       <c r="AB449" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -57642,7 +57642,7 @@
       </c>
       <c r="AB450" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -57764,7 +57764,7 @@
       </c>
       <c r="AB451" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -57896,7 +57896,7 @@
       </c>
       <c r="AB452" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -58018,7 +58018,7 @@
       </c>
       <c r="AB453" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -58140,7 +58140,7 @@
       </c>
       <c r="AB454" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -58268,7 +58268,7 @@
       </c>
       <c r="AB455" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -58396,7 +58396,7 @@
       </c>
       <c r="AB456" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -58518,7 +58518,7 @@
       </c>
       <c r="AB457" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -58650,7 +58650,7 @@
       </c>
       <c r="AB458" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -58772,7 +58772,7 @@
       </c>
       <c r="AB459" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -58894,7 +58894,7 @@
       </c>
       <c r="AB460" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -59016,7 +59016,7 @@
       </c>
       <c r="AB461" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -59144,7 +59144,7 @@
       </c>
       <c r="AB462" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -59272,7 +59272,7 @@
       </c>
       <c r="AB463" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -59400,7 +59400,7 @@
       </c>
       <c r="AB464" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -59522,7 +59522,7 @@
       </c>
       <c r="AB465" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -59650,7 +59650,7 @@
       </c>
       <c r="AB466" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -59778,7 +59778,7 @@
       </c>
       <c r="AB467" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -59900,7 +59900,7 @@
       </c>
       <c r="AB468" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -60028,7 +60028,7 @@
       </c>
       <c r="AB469" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -60150,7 +60150,7 @@
       </c>
       <c r="AB470" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7592,7 +7592,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8238,7 +8238,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8620,7 +8620,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9390,7 +9390,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9640,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9890,7 +9890,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10518,7 +10518,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10890,7 +10890,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11278,7 +11278,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11534,7 +11534,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11912,7 +11912,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12162,7 +12162,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12284,7 +12284,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12416,7 +12416,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12548,7 +12548,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12680,7 +12680,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12802,7 +12802,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13180,7 +13180,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13308,7 +13308,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13436,7 +13436,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13564,7 +13564,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13692,7 +13692,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13948,7 +13948,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14080,7 +14080,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14202,7 +14202,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14330,7 +14330,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14452,7 +14452,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14580,7 +14580,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14840,7 +14840,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14968,7 +14968,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15096,7 +15096,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15218,7 +15218,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15350,7 +15350,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15478,7 +15478,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15862,7 +15862,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15990,7 +15990,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16250,7 +16250,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16382,7 +16382,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16510,7 +16510,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16638,7 +16638,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16770,7 +16770,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16892,7 +16892,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17020,7 +17020,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17142,7 +17142,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17392,7 +17392,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17514,7 +17514,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17642,7 +17642,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17764,7 +17764,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18024,7 +18024,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18152,7 +18152,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18274,7 +18274,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18402,7 +18402,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18530,7 +18530,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18658,7 +18658,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18790,7 +18790,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18918,7 +18918,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19296,7 +19296,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19424,7 +19424,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19546,7 +19546,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19674,7 +19674,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19796,7 +19796,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19918,7 +19918,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -20046,7 +20046,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -20178,7 +20178,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -20310,7 +20310,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -20570,7 +20570,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -20698,7 +20698,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -20830,7 +20830,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -20952,7 +20952,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -21080,7 +21080,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -21208,7 +21208,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -21336,7 +21336,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -21468,7 +21468,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -21724,7 +21724,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -21846,7 +21846,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -21974,7 +21974,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -22102,7 +22102,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -22234,7 +22234,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -22356,7 +22356,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -22484,7 +22484,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -22606,7 +22606,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -22734,7 +22734,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -22866,7 +22866,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -22988,7 +22988,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -23116,7 +23116,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -23244,7 +23244,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -23372,7 +23372,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -23500,7 +23500,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -23628,7 +23628,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -23756,7 +23756,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -23884,7 +23884,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -24006,7 +24006,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -24134,7 +24134,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -24256,7 +24256,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -24384,7 +24384,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -24512,7 +24512,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -24634,7 +24634,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -24762,7 +24762,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -24890,7 +24890,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -25150,7 +25150,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -25278,7 +25278,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -25406,7 +25406,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -25534,7 +25534,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -25662,7 +25662,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -25784,7 +25784,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -25912,7 +25912,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -26044,7 +26044,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -26176,7 +26176,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -26304,7 +26304,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -26426,7 +26426,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -26548,7 +26548,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -26670,7 +26670,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -26798,7 +26798,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -27182,7 +27182,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -27436,7 +27436,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -27568,7 +27568,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -27700,7 +27700,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -27832,7 +27832,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -27960,7 +27960,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -28088,7 +28088,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -28216,7 +28216,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -28344,7 +28344,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -28472,7 +28472,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -28604,7 +28604,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -28726,7 +28726,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -28854,7 +28854,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -28986,7 +28986,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -29114,7 +29114,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -29242,7 +29242,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -29486,7 +29486,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -29614,7 +29614,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -29742,7 +29742,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -29992,7 +29992,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -30120,7 +30120,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -30248,7 +30248,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -30370,7 +30370,7 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -30492,7 +30492,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -30614,7 +30614,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -30736,7 +30736,7 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -30858,7 +30858,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -30986,7 +30986,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -31246,7 +31246,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -31378,7 +31378,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -31510,7 +31510,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -31632,7 +31632,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -31754,7 +31754,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -31882,7 +31882,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -32014,7 +32014,7 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -32142,7 +32142,7 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -32274,7 +32274,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -32402,7 +32402,7 @@
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -32530,7 +32530,7 @@
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -32652,7 +32652,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -32780,7 +32780,7 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -32912,7 +32912,7 @@
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -33034,7 +33034,7 @@
       </c>
       <c r="AB256" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -33156,7 +33156,7 @@
       </c>
       <c r="AB257" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -33284,7 +33284,7 @@
       </c>
       <c r="AB258" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -33406,7 +33406,7 @@
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -33538,7 +33538,7 @@
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -33670,7 +33670,7 @@
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -33792,7 +33792,7 @@
       </c>
       <c r="AB262" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -33914,7 +33914,7 @@
       </c>
       <c r="AB263" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="AB264" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -34178,7 +34178,7 @@
       </c>
       <c r="AB265" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -34310,7 +34310,7 @@
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -34442,7 +34442,7 @@
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -34564,7 +34564,7 @@
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -34692,7 +34692,7 @@
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -34820,7 +34820,7 @@
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -34942,7 +34942,7 @@
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -35070,7 +35070,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -35198,7 +35198,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -35326,7 +35326,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -35454,7 +35454,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -35586,7 +35586,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -35708,7 +35708,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -35836,7 +35836,7 @@
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -35968,7 +35968,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -36096,7 +36096,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -36346,7 +36346,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -36468,7 +36468,7 @@
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -36596,7 +36596,7 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -36728,7 +36728,7 @@
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -36856,7 +36856,7 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -36988,7 +36988,7 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -37120,7 +37120,7 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -37252,7 +37252,7 @@
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -37384,7 +37384,7 @@
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -37516,7 +37516,7 @@
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -37772,7 +37772,7 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -37894,7 +37894,7 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -38016,7 +38016,7 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -38138,7 +38138,7 @@
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -38270,7 +38270,7 @@
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -38402,7 +38402,7 @@
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -38530,7 +38530,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -38652,7 +38652,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -38780,7 +38780,7 @@
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -38902,7 +38902,7 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -39024,7 +39024,7 @@
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -39146,7 +39146,7 @@
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -39278,7 +39278,7 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -39400,7 +39400,7 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -39532,7 +39532,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -39654,7 +39654,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -39776,7 +39776,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -39904,7 +39904,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -40032,7 +40032,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -40164,7 +40164,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -40286,7 +40286,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -40408,7 +40408,7 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -40540,7 +40540,7 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -40672,7 +40672,7 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -40800,7 +40800,7 @@
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -40928,7 +40928,7 @@
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -41050,7 +41050,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -41182,7 +41182,7 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -41304,7 +41304,7 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -41432,7 +41432,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -41554,7 +41554,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -41676,7 +41676,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -41808,7 +41808,7 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -41940,7 +41940,7 @@
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -42062,7 +42062,7 @@
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -42194,7 +42194,7 @@
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -42322,7 +42322,7 @@
       </c>
       <c r="AB329" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -42444,7 +42444,7 @@
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -42566,7 +42566,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -42698,7 +42698,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -42830,7 +42830,7 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -42958,7 +42958,7 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -43090,7 +43090,7 @@
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -43218,7 +43218,7 @@
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -43350,7 +43350,7 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -43472,7 +43472,7 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -43594,7 +43594,7 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -43716,7 +43716,7 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -43848,7 +43848,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -43970,7 +43970,7 @@
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -44102,7 +44102,7 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -44224,7 +44224,7 @@
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -44352,7 +44352,7 @@
       </c>
       <c r="AB345" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -44484,7 +44484,7 @@
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -44606,7 +44606,7 @@
       </c>
       <c r="AB347" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -44728,7 +44728,7 @@
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -44860,7 +44860,7 @@
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -44988,7 +44988,7 @@
       </c>
       <c r="AB350" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -45110,7 +45110,7 @@
       </c>
       <c r="AB351" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -45232,7 +45232,7 @@
       </c>
       <c r="AB352" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -45354,7 +45354,7 @@
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -45476,7 +45476,7 @@
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -45608,7 +45608,7 @@
       </c>
       <c r="AB355" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -45736,7 +45736,7 @@
       </c>
       <c r="AB356" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -45868,7 +45868,7 @@
       </c>
       <c r="AB357" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -45990,7 +45990,7 @@
       </c>
       <c r="AB358" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -46122,7 +46122,7 @@
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -46254,7 +46254,7 @@
       </c>
       <c r="AB360" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -46376,7 +46376,7 @@
       </c>
       <c r="AB361" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -46504,7 +46504,7 @@
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -46632,7 +46632,7 @@
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -46760,7 +46760,7 @@
       </c>
       <c r="AB364" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -46882,7 +46882,7 @@
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -47010,7 +47010,7 @@
       </c>
       <c r="AB366" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -47132,7 +47132,7 @@
       </c>
       <c r="AB367" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -47260,7 +47260,7 @@
       </c>
       <c r="AB368" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -47382,7 +47382,7 @@
       </c>
       <c r="AB369" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -47514,7 +47514,7 @@
       </c>
       <c r="AB370" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -47636,7 +47636,7 @@
       </c>
       <c r="AB371" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -47764,7 +47764,7 @@
       </c>
       <c r="AB372" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -47896,7 +47896,7 @@
       </c>
       <c r="AB373" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -48028,7 +48028,7 @@
       </c>
       <c r="AB374" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -48156,7 +48156,7 @@
       </c>
       <c r="AB375" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -48288,7 +48288,7 @@
       </c>
       <c r="AB376" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -48420,7 +48420,7 @@
       </c>
       <c r="AB377" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -48548,7 +48548,7 @@
       </c>
       <c r="AB378" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -48670,7 +48670,7 @@
       </c>
       <c r="AB379" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -48792,7 +48792,7 @@
       </c>
       <c r="AB380" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -48924,7 +48924,7 @@
       </c>
       <c r="AB381" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -49056,7 +49056,7 @@
       </c>
       <c r="AB382" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -49188,7 +49188,7 @@
       </c>
       <c r="AB383" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -49310,7 +49310,7 @@
       </c>
       <c r="AB384" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -49442,7 +49442,7 @@
       </c>
       <c r="AB385" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -49570,7 +49570,7 @@
       </c>
       <c r="AB386" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -49702,7 +49702,7 @@
       </c>
       <c r="AB387" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -49824,7 +49824,7 @@
       </c>
       <c r="AB388" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -49956,7 +49956,7 @@
       </c>
       <c r="AB389" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -50084,7 +50084,7 @@
       </c>
       <c r="AB390" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -50206,7 +50206,7 @@
       </c>
       <c r="AB391" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -50334,7 +50334,7 @@
       </c>
       <c r="AB392" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -50456,7 +50456,7 @@
       </c>
       <c r="AB393" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -50584,7 +50584,7 @@
       </c>
       <c r="AB394" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -50712,7 +50712,7 @@
       </c>
       <c r="AB395" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -50834,7 +50834,7 @@
       </c>
       <c r="AB396" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -50956,7 +50956,7 @@
       </c>
       <c r="AB397" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -51078,7 +51078,7 @@
       </c>
       <c r="AB398" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -51200,7 +51200,7 @@
       </c>
       <c r="AB399" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -51322,7 +51322,7 @@
       </c>
       <c r="AB400" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -51444,7 +51444,7 @@
       </c>
       <c r="AB401" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -51572,7 +51572,7 @@
       </c>
       <c r="AB402" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -51700,7 +51700,7 @@
       </c>
       <c r="AB403" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -51832,7 +51832,7 @@
       </c>
       <c r="AB404" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -51964,7 +51964,7 @@
       </c>
       <c r="AB405" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -52086,7 +52086,7 @@
       </c>
       <c r="AB406" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -52208,7 +52208,7 @@
       </c>
       <c r="AB407" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -52340,7 +52340,7 @@
       </c>
       <c r="AB408" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -52472,7 +52472,7 @@
       </c>
       <c r="AB409" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -52594,7 +52594,7 @@
       </c>
       <c r="AB410" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -52722,7 +52722,7 @@
       </c>
       <c r="AB411" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -52854,7 +52854,7 @@
       </c>
       <c r="AB412" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -52986,7 +52986,7 @@
       </c>
       <c r="AB413" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -53108,7 +53108,7 @@
       </c>
       <c r="AB414" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -53236,7 +53236,7 @@
       </c>
       <c r="AB415" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -53368,7 +53368,7 @@
       </c>
       <c r="AB416" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -53500,7 +53500,7 @@
       </c>
       <c r="AB417" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -53632,7 +53632,7 @@
       </c>
       <c r="AB418" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -53754,7 +53754,7 @@
       </c>
       <c r="AB419" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -53886,7 +53886,7 @@
       </c>
       <c r="AB420" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -54008,7 +54008,7 @@
       </c>
       <c r="AB421" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -54130,7 +54130,7 @@
       </c>
       <c r="AB422" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -54252,7 +54252,7 @@
       </c>
       <c r="AB423" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -54374,7 +54374,7 @@
       </c>
       <c r="AB424" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -54496,7 +54496,7 @@
       </c>
       <c r="AB425" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -54628,7 +54628,7 @@
       </c>
       <c r="AB426" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -54760,7 +54760,7 @@
       </c>
       <c r="AB427" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -54882,7 +54882,7 @@
       </c>
       <c r="AB428" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -55004,7 +55004,7 @@
       </c>
       <c r="AB429" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -55126,7 +55126,7 @@
       </c>
       <c r="AB430" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -55248,7 +55248,7 @@
       </c>
       <c r="AB431" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -55380,7 +55380,7 @@
       </c>
       <c r="AB432" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -55512,7 +55512,7 @@
       </c>
       <c r="AB433" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -55644,7 +55644,7 @@
       </c>
       <c r="AB434" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -55766,7 +55766,7 @@
       </c>
       <c r="AB435" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -55888,7 +55888,7 @@
       </c>
       <c r="AB436" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -56020,7 +56020,7 @@
       </c>
       <c r="AB437" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -56152,7 +56152,7 @@
       </c>
       <c r="AB438" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -56274,7 +56274,7 @@
       </c>
       <c r="AB439" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -56406,7 +56406,7 @@
       </c>
       <c r="AB440" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -56528,7 +56528,7 @@
       </c>
       <c r="AB441" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -56650,7 +56650,7 @@
       </c>
       <c r="AB442" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -56778,7 +56778,7 @@
       </c>
       <c r="AB443" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -56900,7 +56900,7 @@
       </c>
       <c r="AB444" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -57022,7 +57022,7 @@
       </c>
       <c r="AB445" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -57154,7 +57154,7 @@
       </c>
       <c r="AB446" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -57276,7 +57276,7 @@
       </c>
       <c r="AB447" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -57398,7 +57398,7 @@
       </c>
       <c r="AB448" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -57520,7 +57520,7 @@
       </c>
       <c r="AB449" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -57642,7 +57642,7 @@
       </c>
       <c r="AB450" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -57764,7 +57764,7 @@
       </c>
       <c r="AB451" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -57896,7 +57896,7 @@
       </c>
       <c r="AB452" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -58018,7 +58018,7 @@
       </c>
       <c r="AB453" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -58140,7 +58140,7 @@
       </c>
       <c r="AB454" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -58268,7 +58268,7 @@
       </c>
       <c r="AB455" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -58396,7 +58396,7 @@
       </c>
       <c r="AB456" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -58518,7 +58518,7 @@
       </c>
       <c r="AB457" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -58650,7 +58650,7 @@
       </c>
       <c r="AB458" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -58772,7 +58772,7 @@
       </c>
       <c r="AB459" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -58894,7 +58894,7 @@
       </c>
       <c r="AB460" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -59016,7 +59016,7 @@
       </c>
       <c r="AB461" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -59144,7 +59144,7 @@
       </c>
       <c r="AB462" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -59272,7 +59272,7 @@
       </c>
       <c r="AB463" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -59400,7 +59400,7 @@
       </c>
       <c r="AB464" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -59522,7 +59522,7 @@
       </c>
       <c r="AB465" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -59650,7 +59650,7 @@
       </c>
       <c r="AB466" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -59778,7 +59778,7 @@
       </c>
       <c r="AB467" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -59900,7 +59900,7 @@
       </c>
       <c r="AB468" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -60028,7 +60028,7 @@
       </c>
       <c r="AB469" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -60150,7 +60150,7 @@
       </c>
       <c r="AB470" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Predue, Brandon, Feilder, Collins &amp; Mott, LLP / Karl W King</t>
+          <t>Predue, Brandon, Feilder, Collins &amp; Mott, LLP / Karina Andrade</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -939,12 +939,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=23-CA-016325</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=23-CA-016325</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1939,12 +1939,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2067,12 +2067,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Karina Andrade / Yolanda Humphrey</t>
+          <t>Linda L. Robinson / Karina Andrade</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2195,12 +2195,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2451,12 +2451,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2579,12 +2579,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Yolanda M Humphrey / Linebarger Goggan Blair Sampson LLP</t>
+          <t>Roy Varghese Panakezham / Blair K Woodard</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2835,12 +2835,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2957,12 +2957,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3085,12 +3085,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3207,12 +3207,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3335,12 +3335,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3591,12 +3591,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3847,12 +3847,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4103,12 +4103,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4231,12 +4231,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4359,12 +4359,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=26-CA-006185</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=26-CA-006185</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4811,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4865,12 +4865,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -4993,12 +4993,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5115,12 +5115,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5243,12 +5243,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5371,12 +5371,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5499,12 +5499,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5627,12 +5627,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6005,12 +6005,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -6133,12 +6133,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6261,12 +6261,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6289,7 +6289,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Alexander Freeman / Eula Webster Freeman</t>
+          <t>Predue Brandon Fielder Collins &amp; Mott LLP / Yolanda M Humphrey</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6517,12 +6517,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6713,7 +6713,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6767,12 +6767,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6841,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6969,7 +6969,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7023,12 +7023,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P53" t="inlineStr"/>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=24-CA-001841</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=24-CA-001841</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7273,12 +7273,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7347,7 +7347,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7401,12 +7401,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7523,12 +7523,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7651,12 +7651,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7779,12 +7779,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -7907,12 +7907,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8109,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8163,12 +8163,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8285,12 +8285,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8413,12 +8413,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8535,12 +8535,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Jovita Cortez Martinez / Gloria Cortez Jasso</t>
+          <t>Guadalupe Cortez / Socorro Cortez Torres</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8791,12 +8791,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -8919,12 +8919,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8989,7 +8989,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -9047,12 +9047,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9169,12 +9169,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9297,12 +9297,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9419,12 +9419,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9541,12 +9541,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P73" t="n">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9743,7 +9743,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9797,12 +9797,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9871,7 +9871,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -9925,12 +9925,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aaron Eugene Pope / Kenyada Pope</t>
+          <t>Rosalyn Denise Pope / Tawaneka Pope</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -10053,12 +10053,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10127,7 +10127,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10181,12 +10181,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10309,12 +10309,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10559,12 +10559,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10687,12 +10687,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -10937,12 +10937,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11011,7 +11011,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11065,12 +11065,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11139,7 +11139,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11193,12 +11193,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11315,12 +11315,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11437,12 +11437,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11511,7 +11511,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11565,12 +11565,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11639,7 +11639,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11767,7 +11767,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11821,12 +11821,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11891,7 +11891,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P91" t="n">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Linbarger Goggan Blair &amp; Sampson LLP / Cinthy Pena</t>
+          <t>Mark Steven Meredith / Cinthy Pena</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P92" t="n">
@@ -12032,7 +12032,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12151,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12205,12 +12205,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12279,7 +12279,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12333,12 +12333,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12407,7 +12407,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12461,12 +12461,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12535,7 +12535,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12589,12 +12589,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P97" t="inlineStr"/>
@@ -12676,7 +12676,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=23-CA-017541</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=23-CA-017541</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -12686,7 +12686,7 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
@@ -12711,12 +12711,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P98" t="n">
@@ -12794,7 +12794,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -12839,12 +12839,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12913,7 +12913,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -12967,12 +12967,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13041,7 +13041,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13095,12 +13095,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13169,7 +13169,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13223,12 +13223,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13297,7 +13297,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13351,12 +13351,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13425,7 +13425,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13479,12 +13479,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13549,7 +13549,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P104" t="inlineStr"/>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=21-CA-005559</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=21-CA-005559</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -13576,7 +13576,7 @@
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W104" t="inlineStr">
@@ -13601,12 +13601,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13675,7 +13675,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13729,12 +13729,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -13857,12 +13857,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13931,7 +13931,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -13985,12 +13985,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14055,7 +14055,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -14068,7 +14068,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -14113,12 +14113,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14183,7 +14183,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -14196,7 +14196,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -14241,12 +14241,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14315,7 +14315,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14369,12 +14369,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14443,7 +14443,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14571,7 +14571,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14625,12 +14625,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14699,7 +14699,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14753,12 +14753,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14827,7 +14827,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -14881,12 +14881,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14951,7 +14951,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -14964,7 +14964,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -15009,12 +15009,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -15083,7 +15083,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15137,12 +15137,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -15255,12 +15255,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15383,12 +15383,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -15511,12 +15511,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -15633,12 +15633,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -15707,7 +15707,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -15761,12 +15761,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -15883,12 +15883,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -16005,12 +16005,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -16079,7 +16079,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16133,12 +16133,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -16207,7 +16207,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16261,12 +16261,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P126" t="n">
@@ -16344,7 +16344,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
@@ -16389,12 +16389,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -16507,12 +16507,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -16577,7 +16577,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -16590,7 +16590,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
@@ -16635,12 +16635,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -16709,7 +16709,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -16763,12 +16763,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -16837,7 +16837,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -16891,12 +16891,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -16965,7 +16965,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -17019,12 +17019,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P132" t="n">
@@ -17102,7 +17102,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -17147,12 +17147,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -17221,7 +17221,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17275,12 +17275,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -17397,12 +17397,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -17471,7 +17471,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -17525,12 +17525,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -17595,7 +17595,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
@@ -17653,12 +17653,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -17775,12 +17775,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -17849,7 +17849,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -17903,12 +17903,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -17973,7 +17973,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P139" t="inlineStr"/>
@@ -17990,7 +17990,7 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=21-CA-004936</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=21-CA-004936</t>
         </is>
       </c>
       <c r="U139" t="inlineStr">
@@ -18000,7 +18000,7 @@
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
@@ -18025,12 +18025,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -18147,12 +18147,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -18221,7 +18221,7 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
@@ -18275,12 +18275,12 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -18349,7 +18349,7 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
@@ -18403,12 +18403,12 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -18477,7 +18477,7 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
@@ -18531,12 +18531,12 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -18605,7 +18605,7 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
@@ -18659,12 +18659,12 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
@@ -18787,12 +18787,12 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -18857,7 +18857,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P146" t="n">
@@ -18870,7 +18870,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S146" t="inlineStr">
@@ -18915,12 +18915,12 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -18989,7 +18989,7 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
@@ -19043,12 +19043,12 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
@@ -19171,12 +19171,12 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P149" t="n">
@@ -19254,7 +19254,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
@@ -19299,12 +19299,12 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -19373,7 +19373,7 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
@@ -19427,12 +19427,12 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -19501,7 +19501,7 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
@@ -19555,12 +19555,12 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -19625,7 +19625,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P152" t="n">
@@ -19638,7 +19638,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
@@ -19683,12 +19683,12 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -19757,7 +19757,7 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
@@ -19811,12 +19811,12 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -19885,7 +19885,7 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -19939,12 +19939,12 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -20013,7 +20013,7 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
@@ -20067,12 +20067,12 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -20141,7 +20141,7 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
@@ -20195,12 +20195,12 @@
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -20265,7 +20265,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P157" t="inlineStr"/>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=23-CA-014882</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=23-CA-014882</t>
         </is>
       </c>
       <c r="U157" t="inlineStr">
@@ -20292,7 +20292,7 @@
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
@@ -20317,12 +20317,12 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -20391,7 +20391,7 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -20445,12 +20445,12 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P159" t="n">
@@ -20528,7 +20528,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
@@ -20573,12 +20573,12 @@
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -20701,12 +20701,12 @@
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -20823,12 +20823,12 @@
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -20893,7 +20893,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P162" t="n">
@@ -20906,7 +20906,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
@@ -20951,12 +20951,12 @@
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -21025,7 +21025,7 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -21079,12 +21079,12 @@
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -21153,7 +21153,7 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
@@ -21207,12 +21207,12 @@
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -21281,7 +21281,7 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -21335,12 +21335,12 @@
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -21409,7 +21409,7 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
@@ -21463,12 +21463,12 @@
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -21537,7 +21537,7 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
@@ -21591,12 +21591,12 @@
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -21665,7 +21665,7 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
@@ -21719,12 +21719,12 @@
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -21841,12 +21841,12 @@
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -21911,7 +21911,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P170" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S170" t="inlineStr">
@@ -21969,12 +21969,12 @@
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -22091,12 +22091,12 @@
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -22165,7 +22165,7 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
@@ -22219,12 +22219,12 @@
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -22289,7 +22289,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P173" t="n">
@@ -22302,7 +22302,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S173" t="inlineStr">
@@ -22347,12 +22347,12 @@
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -22421,7 +22421,7 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
@@ -22475,12 +22475,12 @@
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -22545,7 +22545,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P175" t="n">
@@ -22558,7 +22558,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S175" t="inlineStr">
@@ -22603,12 +22603,12 @@
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P176" t="n">
@@ -22686,7 +22686,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S176" t="inlineStr">
@@ -22731,12 +22731,12 @@
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -22853,12 +22853,12 @@
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -22927,7 +22927,7 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
@@ -22981,12 +22981,12 @@
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P179" t="n">
@@ -23064,7 +23064,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S179" t="inlineStr">
@@ -23109,12 +23109,12 @@
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -23183,7 +23183,7 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
@@ -23237,12 +23237,12 @@
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -23307,7 +23307,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P181" t="n">
@@ -23320,7 +23320,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S181" t="inlineStr">
@@ -23365,12 +23365,12 @@
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -23393,7 +23393,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Rodger Dale Jablonski / Judy Jablonski AKA Judy Marie Torres</t>
+          <t>Dennis Wayne Jablonski Sr / Merlene Joyce Hinsch</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -23435,7 +23435,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P182" t="n">
@@ -23448,7 +23448,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S182" t="inlineStr">
@@ -23493,12 +23493,12 @@
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -23615,12 +23615,12 @@
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -23685,7 +23685,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P184" t="n">
@@ -23698,7 +23698,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S184" t="inlineStr">
@@ -23743,12 +23743,12 @@
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -23817,7 +23817,7 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
@@ -23871,12 +23871,12 @@
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -23945,7 +23945,7 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
@@ -23999,12 +23999,12 @@
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -24069,7 +24069,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P187" t="n">
@@ -24082,7 +24082,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S187" t="inlineStr">
@@ -24127,12 +24127,12 @@
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -24197,7 +24197,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P188" t="inlineStr"/>
@@ -24214,7 +24214,7 @@
       </c>
       <c r="T188" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=26-CA-000549</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=26-CA-000549</t>
         </is>
       </c>
       <c r="U188" t="inlineStr">
@@ -24224,7 +24224,7 @@
       </c>
       <c r="V188" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W188" t="inlineStr">
@@ -24249,12 +24249,12 @@
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -24371,12 +24371,12 @@
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -24445,7 +24445,7 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
@@ -24499,12 +24499,12 @@
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -24573,7 +24573,7 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
@@ -24627,12 +24627,12 @@
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -24701,7 +24701,7 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
@@ -24755,12 +24755,12 @@
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -24829,7 +24829,7 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
@@ -24883,12 +24883,12 @@
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -24957,7 +24957,7 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
@@ -25011,12 +25011,12 @@
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -25085,7 +25085,7 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
@@ -25139,12 +25139,12 @@
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -25213,7 +25213,7 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
@@ -25267,12 +25267,12 @@
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -25341,7 +25341,7 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
@@ -25395,12 +25395,12 @@
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -25465,7 +25465,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P198" t="n">
@@ -25478,7 +25478,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
@@ -25523,12 +25523,12 @@
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -25551,7 +25551,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Shawn Welch / Charles Welch</t>
+          <t>Jerri Lewis AKA Jerri Lea Lewis (3rd Address) / Jerri Lewis AKA Jerri Lea Lewis (4th Address)</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P199" t="n">
@@ -25606,7 +25606,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S199" t="inlineStr">
@@ -25651,12 +25651,12 @@
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -25721,7 +25721,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P200" t="n">
@@ -25734,7 +25734,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S200" t="inlineStr">
@@ -25779,12 +25779,12 @@
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -25853,7 +25853,7 @@
         </is>
       </c>
       <c r="P201" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
@@ -25907,12 +25907,12 @@
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -25977,7 +25977,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P202" t="n">
@@ -25990,7 +25990,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
@@ -26035,12 +26035,12 @@
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -26109,7 +26109,7 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
@@ -26163,12 +26163,12 @@
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -26237,7 +26237,7 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
@@ -26291,12 +26291,12 @@
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -26365,7 +26365,7 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
@@ -26419,12 +26419,12 @@
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -26493,7 +26493,7 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
@@ -26547,12 +26547,12 @@
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -26617,7 +26617,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P207" t="n">
@@ -26630,7 +26630,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S207" t="inlineStr">
@@ -26675,12 +26675,12 @@
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -26745,7 +26745,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P208" t="inlineStr"/>
@@ -26762,7 +26762,7 @@
       </c>
       <c r="T208" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=25-CA-002135</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=25-CA-002135</t>
         </is>
       </c>
       <c r="U208" t="inlineStr">
@@ -26772,7 +26772,7 @@
       </c>
       <c r="V208" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W208" t="inlineStr">
@@ -26797,12 +26797,12 @@
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -26867,7 +26867,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P209" t="inlineStr"/>
@@ -26884,7 +26884,7 @@
       </c>
       <c r="T209" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=22-CA-008602</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=22-CA-008602</t>
         </is>
       </c>
       <c r="U209" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="V209" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W209" t="inlineStr">
@@ -26919,12 +26919,12 @@
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -26989,7 +26989,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P210" t="n">
@@ -27002,7 +27002,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S210" t="inlineStr">
@@ -27047,12 +27047,12 @@
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -27121,7 +27121,7 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q211" t="inlineStr">
         <is>
@@ -27175,12 +27175,12 @@
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -27245,7 +27245,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P212" t="n">
@@ -27258,7 +27258,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S212" t="inlineStr">
@@ -27303,12 +27303,12 @@
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -27373,7 +27373,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P213" t="n">
@@ -27386,7 +27386,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S213" t="inlineStr">
@@ -27431,12 +27431,12 @@
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -27505,7 +27505,7 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
@@ -27559,12 +27559,12 @@
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -27681,12 +27681,12 @@
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -27751,7 +27751,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P216" t="n">
@@ -27764,7 +27764,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
@@ -27809,12 +27809,12 @@
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -27879,7 +27879,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P217" t="n">
@@ -27892,7 +27892,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
@@ -27937,12 +27937,12 @@
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
@@ -28065,12 +28065,12 @@
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -28139,7 +28139,7 @@
         </is>
       </c>
       <c r="P219" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
@@ -28193,12 +28193,12 @@
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -28267,7 +28267,7 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
@@ -28321,12 +28321,12 @@
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -28443,12 +28443,12 @@
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -28517,7 +28517,7 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q222" t="inlineStr">
         <is>
@@ -28571,12 +28571,12 @@
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -28645,7 +28645,7 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
@@ -28699,12 +28699,12 @@
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -28773,7 +28773,7 @@
         </is>
       </c>
       <c r="P224" t="n">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
@@ -28827,12 +28827,12 @@
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -28901,7 +28901,7 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
@@ -28955,12 +28955,12 @@
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -29029,7 +29029,7 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
@@ -29083,12 +29083,12 @@
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -29157,7 +29157,7 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="Q227" t="inlineStr">
         <is>
@@ -29211,12 +29211,12 @@
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -29333,12 +29333,12 @@
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29407,7 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q229" t="inlineStr">
         <is>
@@ -29461,12 +29461,12 @@
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -29535,7 +29535,7 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q230" t="inlineStr">
         <is>
@@ -29589,12 +29589,12 @@
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -29659,7 +29659,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P231" t="n">
@@ -29672,7 +29672,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S231" t="inlineStr">
@@ -29717,12 +29717,12 @@
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -29791,7 +29791,7 @@
         </is>
       </c>
       <c r="P232" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q232" t="inlineStr">
         <is>
@@ -29845,12 +29845,12 @@
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -29919,7 +29919,7 @@
         </is>
       </c>
       <c r="P233" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q233" t="inlineStr">
         <is>
@@ -29973,12 +29973,12 @@
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -30095,12 +30095,12 @@
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -30165,7 +30165,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P235" t="inlineStr"/>
@@ -30182,7 +30182,7 @@
       </c>
       <c r="T235" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=26-CA-007844</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=26-CA-007844</t>
         </is>
       </c>
       <c r="U235" t="inlineStr">
@@ -30192,7 +30192,7 @@
       </c>
       <c r="V235" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W235" t="inlineStr">
@@ -30217,12 +30217,12 @@
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -30291,7 +30291,7 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="Q236" t="inlineStr">
         <is>
@@ -30345,12 +30345,12 @@
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -30419,7 +30419,7 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q237" t="inlineStr">
         <is>
@@ -30473,12 +30473,12 @@
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -30547,7 +30547,7 @@
         </is>
       </c>
       <c r="P238" t="n">
-        <v>-114</v>
+        <v>-115</v>
       </c>
       <c r="Q238" t="inlineStr">
         <is>
@@ -30601,12 +30601,12 @@
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -30675,7 +30675,7 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="Q239" t="inlineStr">
         <is>
@@ -30729,12 +30729,12 @@
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -30799,7 +30799,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P240" t="inlineStr"/>
@@ -30816,7 +30816,7 @@
       </c>
       <c r="T240" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=18-CA-007512</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=18-CA-007512</t>
         </is>
       </c>
       <c r="U240" t="inlineStr">
@@ -30826,7 +30826,7 @@
       </c>
       <c r="V240" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W240" t="inlineStr">
@@ -30851,12 +30851,12 @@
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P241" t="n">
@@ -30934,7 +30934,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S241" t="inlineStr">
@@ -30979,12 +30979,12 @@
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -31053,7 +31053,7 @@
         </is>
       </c>
       <c r="P242" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q242" t="inlineStr">
         <is>
@@ -31107,12 +31107,12 @@
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -31229,12 +31229,12 @@
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -31303,7 +31303,7 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
@@ -31357,12 +31357,12 @@
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -31385,7 +31385,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Cynthia Garner / Falisha Garner Booker</t>
+          <t>Kimani Garner / Cynthia Garner</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -31427,7 +31427,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P245" t="n">
@@ -31440,7 +31440,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S245" t="inlineStr">
@@ -31485,12 +31485,12 @@
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -31559,7 +31559,7 @@
         </is>
       </c>
       <c r="P246" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
@@ -31613,12 +31613,12 @@
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -31687,7 +31687,7 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
@@ -31741,12 +31741,12 @@
       </c>
       <c r="AA247" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -31815,7 +31815,7 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
@@ -31869,12 +31869,12 @@
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -31943,7 +31943,7 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
@@ -31997,12 +31997,12 @@
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -32071,7 +32071,7 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
@@ -32125,12 +32125,12 @@
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -32153,7 +32153,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>George Solomon / David Solomon</t>
+          <t>Hopie Solomon / Jehu Solomon</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -32195,7 +32195,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P251" t="n">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S251" t="inlineStr">
@@ -32253,12 +32253,12 @@
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -32281,7 +32281,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Aracely Acuna / Santos Martinez</t>
+          <t>Ricardo Sosa Jr / Dolores Sosa Munoz</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -32323,7 +32323,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P252" t="n">
@@ -32336,7 +32336,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S252" t="inlineStr">
@@ -32381,12 +32381,12 @@
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -32455,7 +32455,7 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
@@ -32509,12 +32509,12 @@
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -32583,7 +32583,7 @@
         </is>
       </c>
       <c r="P254" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
@@ -32637,12 +32637,12 @@
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -32665,7 +32665,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Lantanya Simmons / Mable Roberts</t>
+          <t>Raymond Roberts Jr / Gerrell Roberts</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -32707,7 +32707,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P255" t="n">
@@ -32720,7 +32720,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S255" t="inlineStr">
@@ -32765,12 +32765,12 @@
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -32839,7 +32839,7 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
@@ -32893,12 +32893,12 @@
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB256" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -32967,7 +32967,7 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="Q257" t="inlineStr">
         <is>
@@ -33021,12 +33021,12 @@
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB257" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -33095,7 +33095,7 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="Q258" t="inlineStr">
         <is>
@@ -33149,12 +33149,12 @@
       </c>
       <c r="AA258" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB258" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -33223,7 +33223,7 @@
         </is>
       </c>
       <c r="P259" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q259" t="inlineStr">
         <is>
@@ -33277,12 +33277,12 @@
       </c>
       <c r="AA259" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -33351,7 +33351,7 @@
         </is>
       </c>
       <c r="P260" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q260" t="inlineStr">
         <is>
@@ -33405,12 +33405,12 @@
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -33433,7 +33433,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Cruz Valencia (2nd Address) (Returned Undeliverable) / Daniel Valencia (2nd Address)</t>
+          <t>Cruz Valencia (2nd Address) (Returned Undeliverable) / Valenica Cruz</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -33475,7 +33475,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P261" t="n">
@@ -33488,7 +33488,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S261" t="inlineStr">
@@ -33533,12 +33533,12 @@
       </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -33603,7 +33603,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P262" t="n">
@@ -33616,7 +33616,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S262" t="inlineStr">
@@ -33661,12 +33661,12 @@
       </c>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB262" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -33779,12 +33779,12 @@
       </c>
       <c r="AA263" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB263" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -33853,7 +33853,7 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q264" t="inlineStr">
         <is>
@@ -33907,12 +33907,12 @@
       </c>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB264" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -33981,7 +33981,7 @@
         </is>
       </c>
       <c r="P265" t="n">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="Q265" t="inlineStr">
         <is>
@@ -34035,12 +34035,12 @@
       </c>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB265" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -34109,7 +34109,7 @@
         </is>
       </c>
       <c r="P266" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q266" t="inlineStr">
         <is>
@@ -34163,12 +34163,12 @@
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -34281,12 +34281,12 @@
       </c>
       <c r="AA267" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -34355,7 +34355,7 @@
         </is>
       </c>
       <c r="P268" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q268" t="inlineStr">
         <is>
@@ -34409,12 +34409,12 @@
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -34483,7 +34483,7 @@
         </is>
       </c>
       <c r="P269" t="n">
-        <v>-149</v>
+        <v>-150</v>
       </c>
       <c r="Q269" t="inlineStr">
         <is>
@@ -34537,12 +34537,12 @@
       </c>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -34611,7 +34611,7 @@
         </is>
       </c>
       <c r="P270" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="Q270" t="inlineStr">
         <is>
@@ -34665,12 +34665,12 @@
       </c>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -34787,12 +34787,12 @@
       </c>
       <c r="AA271" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -34861,7 +34861,7 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q272" t="inlineStr">
         <is>
@@ -34915,12 +34915,12 @@
       </c>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -34989,7 +34989,7 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
@@ -35043,12 +35043,12 @@
       </c>
       <c r="AA273" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -35117,7 +35117,7 @@
         </is>
       </c>
       <c r="P274" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
@@ -35171,12 +35171,12 @@
       </c>
       <c r="AA274" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -35241,7 +35241,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P275" t="inlineStr"/>
@@ -35258,7 +35258,7 @@
       </c>
       <c r="T275" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=09-CA-009881</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=09-CA-009881</t>
         </is>
       </c>
       <c r="U275" t="inlineStr">
@@ -35268,7 +35268,7 @@
       </c>
       <c r="V275" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W275" t="inlineStr">
@@ -35293,12 +35293,12 @@
       </c>
       <c r="AA275" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -35367,7 +35367,7 @@
         </is>
       </c>
       <c r="P276" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
@@ -35421,12 +35421,12 @@
       </c>
       <c r="AA276" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -35495,7 +35495,7 @@
         </is>
       </c>
       <c r="P277" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q277" t="inlineStr">
         <is>
@@ -35549,12 +35549,12 @@
       </c>
       <c r="AA277" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -35619,7 +35619,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P278" t="n">
@@ -35632,7 +35632,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S278" t="inlineStr">
@@ -35677,12 +35677,12 @@
       </c>
       <c r="AA278" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -35747,7 +35747,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P279" t="n">
@@ -35760,7 +35760,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S279" t="inlineStr">
@@ -35805,12 +35805,12 @@
       </c>
       <c r="AA279" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -35879,7 +35879,7 @@
         </is>
       </c>
       <c r="P280" t="n">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q280" t="inlineStr">
         <is>
@@ -35933,12 +35933,12 @@
       </c>
       <c r="AA280" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -35961,7 +35961,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Donato W Benitez / Elisa Benitez</t>
+          <t>Elisa Benitez / Donato W Benitez</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -36003,7 +36003,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P281" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S281" t="inlineStr">
@@ -36061,12 +36061,12 @@
       </c>
       <c r="AA281" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -36135,7 +36135,7 @@
         </is>
       </c>
       <c r="P282" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
@@ -36189,12 +36189,12 @@
       </c>
       <c r="AA282" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -36263,7 +36263,7 @@
         </is>
       </c>
       <c r="P283" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q283" t="inlineStr">
         <is>
@@ -36317,12 +36317,12 @@
       </c>
       <c r="AA283" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -36391,7 +36391,7 @@
         </is>
       </c>
       <c r="P284" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q284" t="inlineStr">
         <is>
@@ -36445,12 +36445,12 @@
       </c>
       <c r="AA284" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -36515,7 +36515,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P285" t="n">
@@ -36528,7 +36528,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S285" t="inlineStr">
@@ -36573,12 +36573,12 @@
       </c>
       <c r="AA285" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -36643,7 +36643,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P286" t="inlineStr"/>
@@ -36660,7 +36660,7 @@
       </c>
       <c r="T286" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=24-CA-000685</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=24-CA-000685</t>
         </is>
       </c>
       <c r="U286" t="inlineStr">
@@ -36670,7 +36670,7 @@
       </c>
       <c r="V286" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W286" t="inlineStr">
@@ -36695,12 +36695,12 @@
       </c>
       <c r="AA286" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -36769,7 +36769,7 @@
         </is>
       </c>
       <c r="P287" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q287" t="inlineStr">
         <is>
@@ -36823,12 +36823,12 @@
       </c>
       <c r="AA287" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -36897,7 +36897,7 @@
         </is>
       </c>
       <c r="P288" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="Q288" t="inlineStr">
         <is>
@@ -36951,12 +36951,12 @@
       </c>
       <c r="AA288" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -37021,7 +37021,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P289" t="n">
@@ -37034,7 +37034,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S289" t="inlineStr">
@@ -37079,12 +37079,12 @@
       </c>
       <c r="AA289" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -37153,7 +37153,7 @@
         </is>
       </c>
       <c r="P290" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q290" t="inlineStr">
         <is>
@@ -37207,12 +37207,12 @@
       </c>
       <c r="AA290" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -37277,7 +37277,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P291" t="n">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S291" t="inlineStr">
@@ -37335,12 +37335,12 @@
       </c>
       <c r="AA291" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -37409,7 +37409,7 @@
         </is>
       </c>
       <c r="P292" t="n">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="Q292" t="inlineStr">
         <is>
@@ -37463,12 +37463,12 @@
       </c>
       <c r="AA292" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -37537,7 +37537,7 @@
         </is>
       </c>
       <c r="P293" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="Q293" t="inlineStr">
         <is>
@@ -37591,12 +37591,12 @@
       </c>
       <c r="AA293" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -37713,12 +37713,12 @@
       </c>
       <c r="AA294" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -37787,7 +37787,7 @@
         </is>
       </c>
       <c r="P295" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q295" t="inlineStr">
         <is>
@@ -37841,12 +37841,12 @@
       </c>
       <c r="AA295" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -37911,7 +37911,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P296" t="n">
@@ -37924,7 +37924,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S296" t="inlineStr">
@@ -37969,12 +37969,12 @@
       </c>
       <c r="AA296" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -38043,7 +38043,7 @@
         </is>
       </c>
       <c r="P297" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q297" t="inlineStr">
         <is>
@@ -38097,12 +38097,12 @@
       </c>
       <c r="AA297" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -38167,7 +38167,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P298" t="inlineStr"/>
@@ -38184,7 +38184,7 @@
       </c>
       <c r="T298" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=24-CA-005012</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=24-CA-005012</t>
         </is>
       </c>
       <c r="U298" t="inlineStr">
@@ -38194,7 +38194,7 @@
       </c>
       <c r="V298" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W298" t="inlineStr">
@@ -38219,12 +38219,12 @@
       </c>
       <c r="AA298" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -38293,7 +38293,7 @@
         </is>
       </c>
       <c r="P299" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q299" t="inlineStr">
         <is>
@@ -38347,12 +38347,12 @@
       </c>
       <c r="AA299" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -38421,7 +38421,7 @@
         </is>
       </c>
       <c r="P300" t="n">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q300" t="inlineStr">
         <is>
@@ -38475,12 +38475,12 @@
       </c>
       <c r="AA300" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -38593,12 +38593,12 @@
       </c>
       <c r="AA301" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -38667,7 +38667,7 @@
         </is>
       </c>
       <c r="P302" t="n">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="Q302" t="inlineStr">
         <is>
@@ -38721,12 +38721,12 @@
       </c>
       <c r="AA302" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -38795,7 +38795,7 @@
         </is>
       </c>
       <c r="P303" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q303" t="inlineStr">
         <is>
@@ -38849,12 +38849,12 @@
       </c>
       <c r="AA303" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -38923,7 +38923,7 @@
         </is>
       </c>
       <c r="P304" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="Q304" t="inlineStr">
         <is>
@@ -38977,12 +38977,12 @@
       </c>
       <c r="AA304" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -39099,12 +39099,12 @@
       </c>
       <c r="AA305" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -39173,7 +39173,7 @@
         </is>
       </c>
       <c r="P306" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q306" t="inlineStr">
         <is>
@@ -39227,12 +39227,12 @@
       </c>
       <c r="AA306" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -39301,7 +39301,7 @@
         </is>
       </c>
       <c r="P307" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q307" t="inlineStr">
         <is>
@@ -39355,12 +39355,12 @@
       </c>
       <c r="AA307" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -39425,7 +39425,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P308" t="n">
@@ -39438,7 +39438,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S308" t="inlineStr">
@@ -39483,12 +39483,12 @@
       </c>
       <c r="AA308" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -39557,7 +39557,7 @@
         </is>
       </c>
       <c r="P309" t="n">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="Q309" t="inlineStr">
         <is>
@@ -39611,12 +39611,12 @@
       </c>
       <c r="AA309" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -39685,7 +39685,7 @@
         </is>
       </c>
       <c r="P310" t="n">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q310" t="inlineStr">
         <is>
@@ -39739,12 +39739,12 @@
       </c>
       <c r="AA310" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -39813,7 +39813,7 @@
         </is>
       </c>
       <c r="P311" t="n">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q311" t="inlineStr">
         <is>
@@ -39867,12 +39867,12 @@
       </c>
       <c r="AA311" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -39937,7 +39937,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P312" t="n">
@@ -39950,7 +39950,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S312" t="inlineStr">
@@ -39995,12 +39995,12 @@
       </c>
       <c r="AA312" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -40069,7 +40069,7 @@
         </is>
       </c>
       <c r="P313" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q313" t="inlineStr">
         <is>
@@ -40123,12 +40123,12 @@
       </c>
       <c r="AA313" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -40197,7 +40197,7 @@
         </is>
       </c>
       <c r="P314" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q314" t="inlineStr">
         <is>
@@ -40251,12 +40251,12 @@
       </c>
       <c r="AA314" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -40325,7 +40325,7 @@
         </is>
       </c>
       <c r="P315" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q315" t="inlineStr">
         <is>
@@ -40379,12 +40379,12 @@
       </c>
       <c r="AA315" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -40453,7 +40453,7 @@
         </is>
       </c>
       <c r="P316" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q316" t="inlineStr">
         <is>
@@ -40507,12 +40507,12 @@
       </c>
       <c r="AA316" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -40577,7 +40577,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P317" t="n">
@@ -40590,7 +40590,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S317" t="inlineStr">
@@ -40635,12 +40635,12 @@
       </c>
       <c r="AA317" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -40709,7 +40709,7 @@
         </is>
       </c>
       <c r="P318" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q318" t="inlineStr">
         <is>
@@ -40763,12 +40763,12 @@
       </c>
       <c r="AA318" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -40837,7 +40837,7 @@
         </is>
       </c>
       <c r="P319" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q319" t="inlineStr">
         <is>
@@ -40891,12 +40891,12 @@
       </c>
       <c r="AA319" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -40965,7 +40965,7 @@
         </is>
       </c>
       <c r="P320" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q320" t="inlineStr">
         <is>
@@ -41019,12 +41019,12 @@
       </c>
       <c r="AA320" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -41093,7 +41093,7 @@
         </is>
       </c>
       <c r="P321" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q321" t="inlineStr">
         <is>
@@ -41147,12 +41147,12 @@
       </c>
       <c r="AA321" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -41221,7 +41221,7 @@
         </is>
       </c>
       <c r="P322" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q322" t="inlineStr">
         <is>
@@ -41275,12 +41275,12 @@
       </c>
       <c r="AA322" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -41349,7 +41349,7 @@
         </is>
       </c>
       <c r="P323" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q323" t="inlineStr">
         <is>
@@ -41403,12 +41403,12 @@
       </c>
       <c r="AA323" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -41477,7 +41477,7 @@
         </is>
       </c>
       <c r="P324" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q324" t="inlineStr">
         <is>
@@ -41531,12 +41531,12 @@
       </c>
       <c r="AA324" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -41601,7 +41601,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P325" t="n">
@@ -41614,7 +41614,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S325" t="inlineStr">
@@ -41659,12 +41659,12 @@
       </c>
       <c r="AA325" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -41733,7 +41733,7 @@
         </is>
       </c>
       <c r="P326" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q326" t="inlineStr">
         <is>
@@ -41787,12 +41787,12 @@
       </c>
       <c r="AA326" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -41861,7 +41861,7 @@
         </is>
       </c>
       <c r="P327" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q327" t="inlineStr">
         <is>
@@ -41915,12 +41915,12 @@
       </c>
       <c r="AA327" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -41985,7 +41985,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P328" t="n">
@@ -41998,7 +41998,7 @@
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S328" t="inlineStr">
@@ -42043,12 +42043,12 @@
       </c>
       <c r="AA328" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -42117,7 +42117,7 @@
         </is>
       </c>
       <c r="P329" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q329" t="inlineStr">
         <is>
@@ -42171,12 +42171,12 @@
       </c>
       <c r="AA329" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB329" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -42245,7 +42245,7 @@
         </is>
       </c>
       <c r="P330" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q330" t="inlineStr">
         <is>
@@ -42299,12 +42299,12 @@
       </c>
       <c r="AA330" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -42327,7 +42327,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Virgie Washington AKA Virgil Lee Washington AKA Vigia Washington / Thelma Lott</t>
+          <t>Mary Ann Boldin AKA Mary An Bouldin / Sharon M. Lott AKA Sharon M Gray AKA Sharon Lott Gray</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -42369,7 +42369,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P331" t="n">
@@ -42382,7 +42382,7 @@
       </c>
       <c r="R331" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S331" t="inlineStr">
@@ -42427,12 +42427,12 @@
       </c>
       <c r="AA331" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -42501,7 +42501,7 @@
         </is>
       </c>
       <c r="P332" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q332" t="inlineStr">
         <is>
@@ -42555,12 +42555,12 @@
       </c>
       <c r="AA332" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -42629,7 +42629,7 @@
         </is>
       </c>
       <c r="P333" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q333" t="inlineStr">
         <is>
@@ -42683,12 +42683,12 @@
       </c>
       <c r="AA333" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -42757,7 +42757,7 @@
         </is>
       </c>
       <c r="P334" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q334" t="inlineStr">
         <is>
@@ -42811,12 +42811,12 @@
       </c>
       <c r="AA334" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -42885,7 +42885,7 @@
         </is>
       </c>
       <c r="P335" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q335" t="inlineStr">
         <is>
@@ -42939,12 +42939,12 @@
       </c>
       <c r="AA335" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -43009,7 +43009,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P336" t="inlineStr"/>
@@ -43026,7 +43026,7 @@
       </c>
       <c r="T336" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=23-CA-000671</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=23-CA-000671</t>
         </is>
       </c>
       <c r="U336" t="inlineStr">
@@ -43036,7 +43036,7 @@
       </c>
       <c r="V336" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W336" t="inlineStr">
@@ -43061,12 +43061,12 @@
       </c>
       <c r="AA336" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -43135,7 +43135,7 @@
         </is>
       </c>
       <c r="P337" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q337" t="inlineStr">
         <is>
@@ -43189,12 +43189,12 @@
       </c>
       <c r="AA337" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -43263,7 +43263,7 @@
         </is>
       </c>
       <c r="P338" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q338" t="inlineStr">
         <is>
@@ -43317,12 +43317,12 @@
       </c>
       <c r="AA338" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -43387,7 +43387,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P339" t="n">
@@ -43400,7 +43400,7 @@
       </c>
       <c r="R339" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S339" t="inlineStr">
@@ -43445,12 +43445,12 @@
       </c>
       <c r="AA339" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -43519,7 +43519,7 @@
         </is>
       </c>
       <c r="P340" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q340" t="inlineStr">
         <is>
@@ -43573,12 +43573,12 @@
       </c>
       <c r="AA340" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -43647,7 +43647,7 @@
         </is>
       </c>
       <c r="P341" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q341" t="inlineStr">
         <is>
@@ -43701,12 +43701,12 @@
       </c>
       <c r="AA341" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -43775,7 +43775,7 @@
         </is>
       </c>
       <c r="P342" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q342" t="inlineStr">
         <is>
@@ -43829,12 +43829,12 @@
       </c>
       <c r="AA342" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -43903,7 +43903,7 @@
         </is>
       </c>
       <c r="P343" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q343" t="inlineStr">
         <is>
@@ -43957,12 +43957,12 @@
       </c>
       <c r="AA343" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -44031,7 +44031,7 @@
         </is>
       </c>
       <c r="P344" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="Q344" t="inlineStr">
         <is>
@@ -44085,12 +44085,12 @@
       </c>
       <c r="AA344" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -44159,7 +44159,7 @@
         </is>
       </c>
       <c r="P345" t="n">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="Q345" t="inlineStr">
         <is>
@@ -44213,12 +44213,12 @@
       </c>
       <c r="AA345" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB345" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -44287,7 +44287,7 @@
         </is>
       </c>
       <c r="P346" t="n">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="Q346" t="inlineStr">
         <is>
@@ -44341,12 +44341,12 @@
       </c>
       <c r="AA346" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -44415,7 +44415,7 @@
         </is>
       </c>
       <c r="P347" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q347" t="inlineStr">
         <is>
@@ -44469,12 +44469,12 @@
       </c>
       <c r="AA347" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB347" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -44543,7 +44543,7 @@
         </is>
       </c>
       <c r="P348" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q348" t="inlineStr">
         <is>
@@ -44597,12 +44597,12 @@
       </c>
       <c r="AA348" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -44671,7 +44671,7 @@
         </is>
       </c>
       <c r="P349" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q349" t="inlineStr">
         <is>
@@ -44725,12 +44725,12 @@
       </c>
       <c r="AA349" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -44799,7 +44799,7 @@
         </is>
       </c>
       <c r="P350" t="n">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="Q350" t="inlineStr">
         <is>
@@ -44853,12 +44853,12 @@
       </c>
       <c r="AA350" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB350" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -44927,7 +44927,7 @@
         </is>
       </c>
       <c r="P351" t="n">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="Q351" t="inlineStr">
         <is>
@@ -44981,12 +44981,12 @@
       </c>
       <c r="AA351" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB351" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -45055,7 +45055,7 @@
         </is>
       </c>
       <c r="P352" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q352" t="inlineStr">
         <is>
@@ -45109,12 +45109,12 @@
       </c>
       <c r="AA352" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB352" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -45183,7 +45183,7 @@
         </is>
       </c>
       <c r="P353" t="n">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="Q353" t="inlineStr">
         <is>
@@ -45237,12 +45237,12 @@
       </c>
       <c r="AA353" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -45311,7 +45311,7 @@
         </is>
       </c>
       <c r="P354" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q354" t="inlineStr">
         <is>
@@ -45365,12 +45365,12 @@
       </c>
       <c r="AA354" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -45435,7 +45435,7 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P355" t="inlineStr"/>
@@ -45452,7 +45452,7 @@
       </c>
       <c r="T355" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=22-CA-007538</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=22-CA-007538</t>
         </is>
       </c>
       <c r="U355" t="inlineStr">
@@ -45462,7 +45462,7 @@
       </c>
       <c r="V355" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W355" t="inlineStr">
@@ -45487,12 +45487,12 @@
       </c>
       <c r="AA355" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB355" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -45561,7 +45561,7 @@
         </is>
       </c>
       <c r="P356" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q356" t="inlineStr">
         <is>
@@ -45615,12 +45615,12 @@
       </c>
       <c r="AA356" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB356" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -45689,7 +45689,7 @@
         </is>
       </c>
       <c r="P357" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q357" t="inlineStr">
         <is>
@@ -45743,12 +45743,12 @@
       </c>
       <c r="AA357" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB357" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -45817,7 +45817,7 @@
         </is>
       </c>
       <c r="P358" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q358" t="inlineStr">
         <is>
@@ -45871,12 +45871,12 @@
       </c>
       <c r="AA358" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB358" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -45945,7 +45945,7 @@
         </is>
       </c>
       <c r="P359" t="n">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q359" t="inlineStr">
         <is>
@@ -45999,12 +45999,12 @@
       </c>
       <c r="AA359" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -46069,7 +46069,7 @@
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P360" t="n">
@@ -46082,7 +46082,7 @@
       </c>
       <c r="R360" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S360" t="inlineStr">
@@ -46127,12 +46127,12 @@
       </c>
       <c r="AA360" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB360" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -46201,7 +46201,7 @@
         </is>
       </c>
       <c r="P361" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q361" t="inlineStr">
         <is>
@@ -46255,12 +46255,12 @@
       </c>
       <c r="AA361" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB361" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -46377,12 +46377,12 @@
       </c>
       <c r="AA362" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -46451,7 +46451,7 @@
         </is>
       </c>
       <c r="P363" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q363" t="inlineStr">
         <is>
@@ -46505,12 +46505,12 @@
       </c>
       <c r="AA363" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -46579,7 +46579,7 @@
         </is>
       </c>
       <c r="P364" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q364" t="inlineStr">
         <is>
@@ -46633,12 +46633,12 @@
       </c>
       <c r="AA364" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB364" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -46707,7 +46707,7 @@
         </is>
       </c>
       <c r="P365" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q365" t="inlineStr">
         <is>
@@ -46761,12 +46761,12 @@
       </c>
       <c r="AA365" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -46835,7 +46835,7 @@
         </is>
       </c>
       <c r="P366" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q366" t="inlineStr">
         <is>
@@ -46889,12 +46889,12 @@
       </c>
       <c r="AA366" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB366" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -46963,7 +46963,7 @@
         </is>
       </c>
       <c r="P367" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q367" t="inlineStr">
         <is>
@@ -47017,12 +47017,12 @@
       </c>
       <c r="AA367" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB367" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -47091,7 +47091,7 @@
         </is>
       </c>
       <c r="P368" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q368" t="inlineStr">
         <is>
@@ -47145,12 +47145,12 @@
       </c>
       <c r="AA368" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB368" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -47215,7 +47215,7 @@
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P369" t="inlineStr"/>
@@ -47232,7 +47232,7 @@
       </c>
       <c r="T369" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=25-CA-005347</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=25-CA-005347</t>
         </is>
       </c>
       <c r="U369" t="inlineStr">
@@ -47242,7 +47242,7 @@
       </c>
       <c r="V369" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W369" t="inlineStr">
@@ -47267,12 +47267,12 @@
       </c>
       <c r="AA369" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB369" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>

--- a/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Predue, Brandon, Feilder, Collins &amp; Mott, LLP / Karina Andrade</t>
+          <t>Predue, Brandon, Feilder, Collins &amp; Mott, LLP / Karl W King</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -939,12 +939,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=23-CA-016325</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=23-CA-016325</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1939,12 +1939,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2067,12 +2067,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2195,12 +2195,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2451,12 +2451,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2579,12 +2579,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2835,12 +2835,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2957,12 +2957,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3085,12 +3085,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3207,12 +3207,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>J.D. Whitehead / Clive L Sheppard</t>
+          <t>John C. Salmon (2nd Address) / J.D Whitehead (2nd Address) (Returned to Sender)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3335,12 +3335,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Charles F Sherwood / Sam R Casey Sr</t>
+          <t>Robert Randolph Casey Jr / Shawn Russell Casey</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3591,12 +3591,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3847,12 +3847,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sam F Elwood / Vivian Cheney</t>
+          <t>Ivo R Castlio / Sam F. Elwood (2nd Address)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4103,12 +4103,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4231,12 +4231,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4359,12 +4359,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=26-CA-006185</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=26-CA-006185</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4811,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4865,12 +4865,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -4993,12 +4993,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5115,12 +5115,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5243,12 +5243,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5371,12 +5371,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5499,12 +5499,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5627,12 +5627,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6005,12 +6005,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -6133,12 +6133,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6261,12 +6261,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6331,7 +6331,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6517,12 +6517,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6713,7 +6713,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6767,12 +6767,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6841,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6969,7 +6969,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7023,12 +7023,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P53" t="inlineStr"/>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=24-CA-001841</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=24-CA-001841</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7273,12 +7273,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7347,7 +7347,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7401,12 +7401,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7523,12 +7523,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7651,12 +7651,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7779,12 +7779,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -7907,12 +7907,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8109,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8163,12 +8163,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8285,12 +8285,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8413,12 +8413,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8535,12 +8535,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8791,12 +8791,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -8919,12 +8919,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8989,7 +8989,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -9047,12 +9047,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9169,12 +9169,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9297,12 +9297,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9419,12 +9419,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9541,12 +9541,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9569,7 +9569,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Yolanda M Humphrey / Jennifer C Chiang</t>
+          <t>Blaire K Woodard / Walter Cienfuegos</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P73" t="n">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9743,7 +9743,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9797,12 +9797,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9871,7 +9871,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -9925,12 +9925,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -10053,12 +10053,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10127,7 +10127,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10181,12 +10181,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10309,12 +10309,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10559,12 +10559,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10687,12 +10687,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -10937,12 +10937,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11011,7 +11011,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11065,12 +11065,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11139,7 +11139,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11193,12 +11193,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11315,12 +11315,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11437,12 +11437,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11511,7 +11511,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11565,12 +11565,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11639,7 +11639,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11767,7 +11767,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11821,12 +11821,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11891,7 +11891,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P91" t="n">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12019,7 +12019,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P92" t="n">
@@ -12032,7 +12032,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12151,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12205,12 +12205,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12279,7 +12279,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12333,12 +12333,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12407,7 +12407,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12461,12 +12461,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12535,7 +12535,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12589,12 +12589,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P97" t="inlineStr"/>
@@ -12676,7 +12676,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=23-CA-017541</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=23-CA-017541</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -12686,7 +12686,7 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
@@ -12711,12 +12711,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P98" t="n">
@@ -12794,7 +12794,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -12839,12 +12839,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12913,7 +12913,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -12967,12 +12967,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13041,7 +13041,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13095,12 +13095,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13169,7 +13169,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13223,12 +13223,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13297,7 +13297,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13351,12 +13351,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13425,7 +13425,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13479,12 +13479,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13549,7 +13549,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P104" t="inlineStr"/>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=21-CA-005559</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=21-CA-005559</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -13576,7 +13576,7 @@
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W104" t="inlineStr">
@@ -13601,12 +13601,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13675,7 +13675,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13729,12 +13729,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -13857,12 +13857,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13931,7 +13931,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -13985,12 +13985,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14055,7 +14055,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -14068,7 +14068,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -14113,12 +14113,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14183,7 +14183,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -14196,7 +14196,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -14241,12 +14241,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14315,7 +14315,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14369,12 +14369,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14443,7 +14443,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14571,7 +14571,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14625,12 +14625,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14699,7 +14699,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14753,12 +14753,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14827,7 +14827,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -14881,12 +14881,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14951,7 +14951,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -14964,7 +14964,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -15009,12 +15009,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -15083,7 +15083,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15137,12 +15137,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -15255,12 +15255,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15383,12 +15383,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -15511,12 +15511,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -15633,12 +15633,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -15707,7 +15707,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -15761,12 +15761,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -15883,12 +15883,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -16005,12 +16005,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -16079,7 +16079,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16133,12 +16133,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -16207,7 +16207,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16261,12 +16261,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P126" t="n">
@@ -16344,7 +16344,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
@@ -16389,12 +16389,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -16507,12 +16507,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -16577,7 +16577,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -16590,7 +16590,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
@@ -16635,12 +16635,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -16709,7 +16709,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -16763,12 +16763,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -16837,7 +16837,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -16891,12 +16891,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -16965,7 +16965,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -17019,12 +17019,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P132" t="n">
@@ -17102,7 +17102,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -17147,12 +17147,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -17221,7 +17221,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17275,12 +17275,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -17397,12 +17397,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -17471,7 +17471,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -17525,12 +17525,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -17595,7 +17595,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
@@ -17653,12 +17653,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -17775,12 +17775,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -17849,7 +17849,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -17903,12 +17903,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -17973,7 +17973,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P139" t="inlineStr"/>
@@ -17990,7 +17990,7 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=21-CA-004936</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=21-CA-004936</t>
         </is>
       </c>
       <c r="U139" t="inlineStr">
@@ -18000,7 +18000,7 @@
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
@@ -18025,12 +18025,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -18147,12 +18147,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -18221,7 +18221,7 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
@@ -18275,12 +18275,12 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -18349,7 +18349,7 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
@@ -18403,12 +18403,12 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -18477,7 +18477,7 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
@@ -18531,12 +18531,12 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -18605,7 +18605,7 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
@@ -18659,12 +18659,12 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
@@ -18787,12 +18787,12 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -18857,7 +18857,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P146" t="n">
@@ -18870,7 +18870,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S146" t="inlineStr">
@@ -18915,12 +18915,12 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -18989,7 +18989,7 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
@@ -19043,12 +19043,12 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
@@ -19171,12 +19171,12 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P149" t="n">
@@ -19254,7 +19254,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
@@ -19299,12 +19299,12 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -19373,7 +19373,7 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
@@ -19427,12 +19427,12 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -19501,7 +19501,7 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
@@ -19555,12 +19555,12 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -19625,7 +19625,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P152" t="n">
@@ -19638,7 +19638,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
@@ -19683,12 +19683,12 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -19757,7 +19757,7 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
@@ -19811,12 +19811,12 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -19885,7 +19885,7 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -19939,12 +19939,12 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -20013,7 +20013,7 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
@@ -20067,12 +20067,12 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -20141,7 +20141,7 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
@@ -20195,12 +20195,12 @@
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -20265,7 +20265,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P157" t="inlineStr"/>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=23-CA-014882</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=23-CA-014882</t>
         </is>
       </c>
       <c r="U157" t="inlineStr">
@@ -20292,7 +20292,7 @@
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
@@ -20317,12 +20317,12 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -20391,7 +20391,7 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -20445,12 +20445,12 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P159" t="n">
@@ -20528,7 +20528,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
@@ -20573,12 +20573,12 @@
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -20701,12 +20701,12 @@
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -20823,12 +20823,12 @@
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -20893,7 +20893,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P162" t="n">
@@ -20906,7 +20906,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
@@ -20951,12 +20951,12 @@
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -21025,7 +21025,7 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -21079,12 +21079,12 @@
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -21153,7 +21153,7 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
@@ -21207,12 +21207,12 @@
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -21281,7 +21281,7 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -21335,12 +21335,12 @@
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -21409,7 +21409,7 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
@@ -21463,12 +21463,12 @@
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -21537,7 +21537,7 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
@@ -21591,12 +21591,12 @@
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -21665,7 +21665,7 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
@@ -21719,12 +21719,12 @@
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -21841,12 +21841,12 @@
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -21869,7 +21869,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Lyndon M Jones / Linebarger Goggan Blair &amp; Sampson LLP</t>
+          <t>Linebarger Goggan Blair &amp; Sampson LLP / Lyndon M Jones</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -21911,7 +21911,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P170" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S170" t="inlineStr">
@@ -21969,12 +21969,12 @@
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -22091,12 +22091,12 @@
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -22165,7 +22165,7 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
@@ -22219,12 +22219,12 @@
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -22289,7 +22289,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P173" t="n">
@@ -22302,7 +22302,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S173" t="inlineStr">
@@ -22347,12 +22347,12 @@
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -22421,7 +22421,7 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
@@ -22475,12 +22475,12 @@
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -22545,7 +22545,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P175" t="n">
@@ -22558,7 +22558,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S175" t="inlineStr">
@@ -22603,12 +22603,12 @@
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P176" t="n">
@@ -22686,7 +22686,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S176" t="inlineStr">
@@ -22731,12 +22731,12 @@
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -22853,12 +22853,12 @@
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -22927,7 +22927,7 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
@@ -22981,12 +22981,12 @@
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P179" t="n">
@@ -23064,7 +23064,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S179" t="inlineStr">
@@ -23109,12 +23109,12 @@
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -23183,7 +23183,7 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
@@ -23237,12 +23237,12 @@
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -23307,7 +23307,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P181" t="n">
@@ -23320,7 +23320,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S181" t="inlineStr">
@@ -23365,12 +23365,12 @@
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -23393,7 +23393,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Dennis Wayne Jablonski Sr / Merlene Joyce Hinsch</t>
+          <t>Merlene Joyce Hinsch / Peter Victor Jablonski</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -23435,7 +23435,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P182" t="n">
@@ -23448,7 +23448,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S182" t="inlineStr">
@@ -23493,12 +23493,12 @@
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -23615,12 +23615,12 @@
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -23685,7 +23685,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P184" t="n">
@@ -23698,7 +23698,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S184" t="inlineStr">
@@ -23743,12 +23743,12 @@
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -23817,7 +23817,7 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
@@ -23871,12 +23871,12 @@
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -23945,7 +23945,7 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
@@ -23999,12 +23999,12 @@
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -24069,7 +24069,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P187" t="n">
@@ -24082,7 +24082,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S187" t="inlineStr">
@@ -24127,12 +24127,12 @@
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -24197,7 +24197,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P188" t="inlineStr"/>
@@ -24214,7 +24214,7 @@
       </c>
       <c r="T188" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=26-CA-000549</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=26-CA-000549</t>
         </is>
       </c>
       <c r="U188" t="inlineStr">
@@ -24224,7 +24224,7 @@
       </c>
       <c r="V188" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W188" t="inlineStr">
@@ -24249,12 +24249,12 @@
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -24371,12 +24371,12 @@
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -24445,7 +24445,7 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
@@ -24499,12 +24499,12 @@
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -24573,7 +24573,7 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
@@ -24627,12 +24627,12 @@
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -24701,7 +24701,7 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
@@ -24755,12 +24755,12 @@
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -24829,7 +24829,7 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
@@ -24883,12 +24883,12 @@
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -24957,7 +24957,7 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
@@ -25011,12 +25011,12 @@
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -25085,7 +25085,7 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
@@ -25139,12 +25139,12 @@
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -25213,7 +25213,7 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
@@ -25267,12 +25267,12 @@
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -25341,7 +25341,7 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
@@ -25395,12 +25395,12 @@
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -25423,7 +25423,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Jesus Delgado Jr. AKA Jesus Delgado Sr / Juan S. Delgado AKA Juan Silva</t>
+          <t>Simon Delgado / Vicente Delgado</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -25465,7 +25465,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P198" t="n">
@@ -25478,7 +25478,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
@@ -25523,12 +25523,12 @@
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -25551,7 +25551,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Jerri Lewis AKA Jerri Lea Lewis (3rd Address) / Jerri Lewis AKA Jerri Lea Lewis (4th Address)</t>
+          <t>Shawn Welch (3rd Address) / Heather Welch</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P199" t="n">
@@ -25606,7 +25606,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S199" t="inlineStr">
@@ -25651,12 +25651,12 @@
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -25721,7 +25721,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P200" t="n">
@@ -25734,7 +25734,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S200" t="inlineStr">
@@ -25779,12 +25779,12 @@
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -25853,7 +25853,7 @@
         </is>
       </c>
       <c r="P201" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
@@ -25907,12 +25907,12 @@
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -25977,7 +25977,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P202" t="n">
@@ -25990,7 +25990,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
@@ -26035,12 +26035,12 @@
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -26109,7 +26109,7 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
@@ -26163,12 +26163,12 @@
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -26237,7 +26237,7 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
@@ -26291,12 +26291,12 @@
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -26365,7 +26365,7 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
@@ -26419,12 +26419,12 @@
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -26493,7 +26493,7 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
@@ -26547,12 +26547,12 @@
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -26617,7 +26617,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P207" t="n">
@@ -26630,7 +26630,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S207" t="inlineStr">
@@ -26675,12 +26675,12 @@
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -26745,7 +26745,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P208" t="inlineStr"/>
@@ -26762,7 +26762,7 @@
       </c>
       <c r="T208" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=25-CA-002135</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=25-CA-002135</t>
         </is>
       </c>
       <c r="U208" t="inlineStr">
@@ -26772,7 +26772,7 @@
       </c>
       <c r="V208" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W208" t="inlineStr">
@@ -26797,12 +26797,12 @@
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -26867,7 +26867,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P209" t="inlineStr"/>
@@ -26884,7 +26884,7 @@
       </c>
       <c r="T209" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=22-CA-008602</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=22-CA-008602</t>
         </is>
       </c>
       <c r="U209" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="V209" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W209" t="inlineStr">
@@ -26919,12 +26919,12 @@
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -26989,7 +26989,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P210" t="n">
@@ -27002,7 +27002,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S210" t="inlineStr">
@@ -27047,12 +27047,12 @@
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -27121,7 +27121,7 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q211" t="inlineStr">
         <is>
@@ -27175,12 +27175,12 @@
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -27245,7 +27245,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P212" t="n">
@@ -27258,7 +27258,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S212" t="inlineStr">
@@ -27303,12 +27303,12 @@
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -27373,7 +27373,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P213" t="n">
@@ -27386,7 +27386,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S213" t="inlineStr">
@@ -27431,12 +27431,12 @@
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -27505,7 +27505,7 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
@@ -27559,12 +27559,12 @@
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -27681,12 +27681,12 @@
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -27751,7 +27751,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P216" t="n">
@@ -27764,7 +27764,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
@@ -27809,12 +27809,12 @@
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -27879,7 +27879,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P217" t="n">
@@ -27892,7 +27892,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
@@ -27937,12 +27937,12 @@
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
@@ -28065,12 +28065,12 @@
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -28139,7 +28139,7 @@
         </is>
       </c>
       <c r="P219" t="n">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
@@ -28193,12 +28193,12 @@
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -28267,7 +28267,7 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
@@ -28321,12 +28321,12 @@
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -28443,12 +28443,12 @@
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -28517,7 +28517,7 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q222" t="inlineStr">
         <is>
@@ -28571,12 +28571,12 @@
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -28645,7 +28645,7 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
@@ -28699,12 +28699,12 @@
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -28773,7 +28773,7 @@
         </is>
       </c>
       <c r="P224" t="n">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
@@ -28827,12 +28827,12 @@
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -28901,7 +28901,7 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
@@ -28955,12 +28955,12 @@
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -29029,7 +29029,7 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
@@ -29083,12 +29083,12 @@
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -29157,7 +29157,7 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="Q227" t="inlineStr">
         <is>
@@ -29211,12 +29211,12 @@
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -29333,12 +29333,12 @@
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29407,7 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q229" t="inlineStr">
         <is>
@@ -29461,12 +29461,12 @@
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -29535,7 +29535,7 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q230" t="inlineStr">
         <is>
@@ -29589,12 +29589,12 @@
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -29659,7 +29659,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P231" t="n">
@@ -29672,7 +29672,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S231" t="inlineStr">
@@ -29717,12 +29717,12 @@
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -29791,7 +29791,7 @@
         </is>
       </c>
       <c r="P232" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q232" t="inlineStr">
         <is>
@@ -29845,12 +29845,12 @@
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -29919,7 +29919,7 @@
         </is>
       </c>
       <c r="P233" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q233" t="inlineStr">
         <is>
@@ -29973,12 +29973,12 @@
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -30095,12 +30095,12 @@
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -30165,7 +30165,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P235" t="inlineStr"/>
@@ -30182,7 +30182,7 @@
       </c>
       <c r="T235" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=26-CA-007844</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=26-CA-007844</t>
         </is>
       </c>
       <c r="U235" t="inlineStr">
@@ -30192,7 +30192,7 @@
       </c>
       <c r="V235" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W235" t="inlineStr">
@@ -30217,12 +30217,12 @@
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -30291,7 +30291,7 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q236" t="inlineStr">
         <is>
@@ -30345,12 +30345,12 @@
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -30419,7 +30419,7 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q237" t="inlineStr">
         <is>
@@ -30473,12 +30473,12 @@
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -30547,7 +30547,7 @@
         </is>
       </c>
       <c r="P238" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="Q238" t="inlineStr">
         <is>
@@ -30601,12 +30601,12 @@
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -30675,7 +30675,7 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="Q239" t="inlineStr">
         <is>
@@ -30729,12 +30729,12 @@
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -30799,7 +30799,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P240" t="inlineStr"/>
@@ -30816,7 +30816,7 @@
       </c>
       <c r="T240" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=18-CA-007512</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=18-CA-007512</t>
         </is>
       </c>
       <c r="U240" t="inlineStr">
@@ -30826,7 +30826,7 @@
       </c>
       <c r="V240" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W240" t="inlineStr">
@@ -30851,12 +30851,12 @@
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -30879,7 +30879,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Deondra Lynne Jackson / Hattie Mae Neal Sherman</t>
+          <t>Elaine Neal / Ida Mae Neal Sherman</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -30921,7 +30921,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P241" t="n">
@@ -30934,7 +30934,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S241" t="inlineStr">
@@ -30979,12 +30979,12 @@
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -31053,7 +31053,7 @@
         </is>
       </c>
       <c r="P242" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q242" t="inlineStr">
         <is>
@@ -31107,12 +31107,12 @@
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -31229,12 +31229,12 @@
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -31303,7 +31303,7 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
@@ -31357,12 +31357,12 @@
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -31385,7 +31385,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Kimani Garner / Cynthia Garner</t>
+          <t>Falisha Garner Booker / Tracy Garner Tyson</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -31427,7 +31427,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P245" t="n">
@@ -31440,7 +31440,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S245" t="inlineStr">
@@ -31485,12 +31485,12 @@
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -31559,7 +31559,7 @@
         </is>
       </c>
       <c r="P246" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
@@ -31613,12 +31613,12 @@
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -31687,7 +31687,7 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
@@ -31741,12 +31741,12 @@
       </c>
       <c r="AA247" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -31815,7 +31815,7 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
@@ -31869,12 +31869,12 @@
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -31943,7 +31943,7 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
@@ -31997,12 +31997,12 @@
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -32071,7 +32071,7 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
@@ -32125,12 +32125,12 @@
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -32153,7 +32153,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Hopie Solomon / Jehu Solomon</t>
+          <t>David Solomon / George Solomon</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -32195,7 +32195,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P251" t="n">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S251" t="inlineStr">
@@ -32253,12 +32253,12 @@
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -32323,7 +32323,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P252" t="n">
@@ -32336,7 +32336,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S252" t="inlineStr">
@@ -32381,12 +32381,12 @@
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -32455,7 +32455,7 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
@@ -32509,12 +32509,12 @@
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -32583,7 +32583,7 @@
         </is>
       </c>
       <c r="P254" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
@@ -32637,12 +32637,12 @@
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -32665,7 +32665,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Raymond Roberts Jr / Gerrell Roberts</t>
+          <t>Kevin Roberts / Cassandra Nunn</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -32707,7 +32707,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P255" t="n">
@@ -32720,7 +32720,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S255" t="inlineStr">
@@ -32765,12 +32765,12 @@
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -32839,7 +32839,7 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
@@ -32893,12 +32893,12 @@
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB256" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -32967,7 +32967,7 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="Q257" t="inlineStr">
         <is>
@@ -33021,12 +33021,12 @@
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB257" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -33095,7 +33095,7 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="Q258" t="inlineStr">
         <is>
@@ -33149,12 +33149,12 @@
       </c>
       <c r="AA258" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB258" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -33223,7 +33223,7 @@
         </is>
       </c>
       <c r="P259" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q259" t="inlineStr">
         <is>
@@ -33277,12 +33277,12 @@
       </c>
       <c r="AA259" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -33351,7 +33351,7 @@
         </is>
       </c>
       <c r="P260" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q260" t="inlineStr">
         <is>
@@ -33405,12 +33405,12 @@
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -33433,7 +33433,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Cruz Valencia (2nd Address) (Returned Undeliverable) / Valenica Cruz</t>
+          <t>Valenica Cruz / Daniel Valencia</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -33475,7 +33475,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P261" t="n">
@@ -33488,7 +33488,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S261" t="inlineStr">
@@ -33533,12 +33533,12 @@
       </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -33603,7 +33603,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P262" t="n">
@@ -33616,7 +33616,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S262" t="inlineStr">
@@ -33661,12 +33661,12 @@
       </c>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB262" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -33779,12 +33779,12 @@
       </c>
       <c r="AA263" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB263" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -33853,7 +33853,7 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q264" t="inlineStr">
         <is>
@@ -33907,12 +33907,12 @@
       </c>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB264" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -33981,7 +33981,7 @@
         </is>
       </c>
       <c r="P265" t="n">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="Q265" t="inlineStr">
         <is>
@@ -34035,12 +34035,12 @@
       </c>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB265" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -34109,7 +34109,7 @@
         </is>
       </c>
       <c r="P266" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q266" t="inlineStr">
         <is>
@@ -34163,12 +34163,12 @@
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -34281,12 +34281,12 @@
       </c>
       <c r="AA267" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -34355,7 +34355,7 @@
         </is>
       </c>
       <c r="P268" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q268" t="inlineStr">
         <is>
@@ -34409,12 +34409,12 @@
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -34483,7 +34483,7 @@
         </is>
       </c>
       <c r="P269" t="n">
-        <v>-150</v>
+        <v>-151</v>
       </c>
       <c r="Q269" t="inlineStr">
         <is>
@@ -34537,12 +34537,12 @@
       </c>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -34611,7 +34611,7 @@
         </is>
       </c>
       <c r="P270" t="n">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="Q270" t="inlineStr">
         <is>
@@ -34665,12 +34665,12 @@
       </c>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -34787,12 +34787,12 @@
       </c>
       <c r="AA271" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -34861,7 +34861,7 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q272" t="inlineStr">
         <is>
@@ -34915,12 +34915,12 @@
       </c>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -34989,7 +34989,7 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
@@ -35043,12 +35043,12 @@
       </c>
       <c r="AA273" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -35117,7 +35117,7 @@
         </is>
       </c>
       <c r="P274" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
@@ -35171,12 +35171,12 @@
       </c>
       <c r="AA274" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -35241,7 +35241,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P275" t="inlineStr"/>
@@ -35258,7 +35258,7 @@
       </c>
       <c r="T275" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=09-CA-009881</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=09-CA-009881</t>
         </is>
       </c>
       <c r="U275" t="inlineStr">
@@ -35268,7 +35268,7 @@
       </c>
       <c r="V275" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W275" t="inlineStr">
@@ -35293,12 +35293,12 @@
       </c>
       <c r="AA275" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -35367,7 +35367,7 @@
         </is>
       </c>
       <c r="P276" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
@@ -35421,12 +35421,12 @@
       </c>
       <c r="AA276" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -35495,7 +35495,7 @@
         </is>
       </c>
       <c r="P277" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q277" t="inlineStr">
         <is>
@@ -35549,12 +35549,12 @@
       </c>
       <c r="AA277" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -35619,7 +35619,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P278" t="n">
@@ -35632,7 +35632,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S278" t="inlineStr">
@@ -35677,12 +35677,12 @@
       </c>
       <c r="AA278" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -35747,7 +35747,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P279" t="n">
@@ -35760,7 +35760,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S279" t="inlineStr">
@@ -35805,12 +35805,12 @@
       </c>
       <c r="AA279" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -35879,7 +35879,7 @@
         </is>
       </c>
       <c r="P280" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q280" t="inlineStr">
         <is>
@@ -35933,12 +35933,12 @@
       </c>
       <c r="AA280" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -36003,7 +36003,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P281" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S281" t="inlineStr">
@@ -36061,12 +36061,12 @@
       </c>
       <c r="AA281" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -36135,7 +36135,7 @@
         </is>
       </c>
       <c r="P282" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
@@ -36189,12 +36189,12 @@
       </c>
       <c r="AA282" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -36263,7 +36263,7 @@
         </is>
       </c>
       <c r="P283" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q283" t="inlineStr">
         <is>
@@ -36317,12 +36317,12 @@
       </c>
       <c r="AA283" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -36391,7 +36391,7 @@
         </is>
       </c>
       <c r="P284" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q284" t="inlineStr">
         <is>
@@ -36445,12 +36445,12 @@
       </c>
       <c r="AA284" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -36515,7 +36515,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P285" t="n">
@@ -36528,7 +36528,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S285" t="inlineStr">
@@ -36573,12 +36573,12 @@
       </c>
       <c r="AA285" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -36643,7 +36643,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P286" t="inlineStr"/>
@@ -36660,7 +36660,7 @@
       </c>
       <c r="T286" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=24-CA-000685</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=24-CA-000685</t>
         </is>
       </c>
       <c r="U286" t="inlineStr">
@@ -36670,7 +36670,7 @@
       </c>
       <c r="V286" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W286" t="inlineStr">
@@ -36695,12 +36695,12 @@
       </c>
       <c r="AA286" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -36769,7 +36769,7 @@
         </is>
       </c>
       <c r="P287" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q287" t="inlineStr">
         <is>
@@ -36823,12 +36823,12 @@
       </c>
       <c r="AA287" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -36897,7 +36897,7 @@
         </is>
       </c>
       <c r="P288" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q288" t="inlineStr">
         <is>
@@ -36951,12 +36951,12 @@
       </c>
       <c r="AA288" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -37021,7 +37021,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P289" t="n">
@@ -37034,7 +37034,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S289" t="inlineStr">
@@ -37079,12 +37079,12 @@
       </c>
       <c r="AA289" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -37153,7 +37153,7 @@
         </is>
       </c>
       <c r="P290" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q290" t="inlineStr">
         <is>
@@ -37207,12 +37207,12 @@
       </c>
       <c r="AA290" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -37277,7 +37277,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P291" t="n">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S291" t="inlineStr">
@@ -37335,12 +37335,12 @@
       </c>
       <c r="AA291" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -37409,7 +37409,7 @@
         </is>
       </c>
       <c r="P292" t="n">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="Q292" t="inlineStr">
         <is>
@@ -37463,12 +37463,12 @@
       </c>
       <c r="AA292" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -37537,7 +37537,7 @@
         </is>
       </c>
       <c r="P293" t="n">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="Q293" t="inlineStr">
         <is>
@@ -37591,12 +37591,12 @@
       </c>
       <c r="AA293" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -37713,12 +37713,12 @@
       </c>
       <c r="AA294" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -37787,7 +37787,7 @@
         </is>
       </c>
       <c r="P295" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q295" t="inlineStr">
         <is>
@@ -37841,12 +37841,12 @@
       </c>
       <c r="AA295" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -37911,7 +37911,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P296" t="n">
@@ -37924,7 +37924,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S296" t="inlineStr">
@@ -37969,12 +37969,12 @@
       </c>
       <c r="AA296" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -38043,7 +38043,7 @@
         </is>
       </c>
       <c r="P297" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q297" t="inlineStr">
         <is>
@@ -38097,12 +38097,12 @@
       </c>
       <c r="AA297" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -38167,7 +38167,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P298" t="inlineStr"/>
@@ -38184,7 +38184,7 @@
       </c>
       <c r="T298" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=24-CA-005012</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=24-CA-005012</t>
         </is>
       </c>
       <c r="U298" t="inlineStr">
@@ -38194,7 +38194,7 @@
       </c>
       <c r="V298" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W298" t="inlineStr">
@@ -38219,12 +38219,12 @@
       </c>
       <c r="AA298" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -38293,7 +38293,7 @@
         </is>
       </c>
       <c r="P299" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q299" t="inlineStr">
         <is>
@@ -38347,12 +38347,12 @@
       </c>
       <c r="AA299" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -38421,7 +38421,7 @@
         </is>
       </c>
       <c r="P300" t="n">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Q300" t="inlineStr">
         <is>
@@ -38475,12 +38475,12 @@
       </c>
       <c r="AA300" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -38593,12 +38593,12 @@
       </c>
       <c r="AA301" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -38667,7 +38667,7 @@
         </is>
       </c>
       <c r="P302" t="n">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="Q302" t="inlineStr">
         <is>
@@ -38721,12 +38721,12 @@
       </c>
       <c r="AA302" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -38795,7 +38795,7 @@
         </is>
       </c>
       <c r="P303" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q303" t="inlineStr">
         <is>
@@ -38849,12 +38849,12 @@
       </c>
       <c r="AA303" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -38923,7 +38923,7 @@
         </is>
       </c>
       <c r="P304" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q304" t="inlineStr">
         <is>
@@ -38977,12 +38977,12 @@
       </c>
       <c r="AA304" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -39099,12 +39099,12 @@
       </c>
       <c r="AA305" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -39173,7 +39173,7 @@
         </is>
       </c>
       <c r="P306" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q306" t="inlineStr">
         <is>
@@ -39227,12 +39227,12 @@
       </c>
       <c r="AA306" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -39301,7 +39301,7 @@
         </is>
       </c>
       <c r="P307" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q307" t="inlineStr">
         <is>
@@ -39355,12 +39355,12 @@
       </c>
       <c r="AA307" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -39383,7 +39383,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Freddie Hatton / Gwendolyn Tatum</t>
+          <t>Larry E Spates / Gwendolyn Tatum</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -39425,7 +39425,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P308" t="n">
@@ -39438,7 +39438,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S308" t="inlineStr">
@@ -39483,12 +39483,12 @@
       </c>
       <c r="AA308" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -39557,7 +39557,7 @@
         </is>
       </c>
       <c r="P309" t="n">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Q309" t="inlineStr">
         <is>
@@ -39611,12 +39611,12 @@
       </c>
       <c r="AA309" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -39685,7 +39685,7 @@
         </is>
       </c>
       <c r="P310" t="n">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Q310" t="inlineStr">
         <is>
@@ -39739,12 +39739,12 @@
       </c>
       <c r="AA310" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -39813,7 +39813,7 @@
         </is>
       </c>
       <c r="P311" t="n">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q311" t="inlineStr">
         <is>
@@ -39867,12 +39867,12 @@
       </c>
       <c r="AA311" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -39895,7 +39895,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Linebarger Goggan Blair &amp; Sampson / Dororothy M Davis</t>
+          <t>Dororothy M Davis / Johnny L Davis</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -39937,7 +39937,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P312" t="n">
@@ -39950,7 +39950,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S312" t="inlineStr">
@@ -39995,12 +39995,12 @@
       </c>
       <c r="AA312" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -40069,7 +40069,7 @@
         </is>
       </c>
       <c r="P313" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q313" t="inlineStr">
         <is>
@@ -40123,12 +40123,12 @@
       </c>
       <c r="AA313" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -40197,7 +40197,7 @@
         </is>
       </c>
       <c r="P314" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q314" t="inlineStr">
         <is>
@@ -40251,12 +40251,12 @@
       </c>
       <c r="AA314" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -40325,7 +40325,7 @@
         </is>
       </c>
       <c r="P315" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q315" t="inlineStr">
         <is>
@@ -40379,12 +40379,12 @@
       </c>
       <c r="AA315" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -40453,7 +40453,7 @@
         </is>
       </c>
       <c r="P316" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q316" t="inlineStr">
         <is>
@@ -40507,12 +40507,12 @@
       </c>
       <c r="AA316" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -40577,7 +40577,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P317" t="n">
@@ -40590,7 +40590,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S317" t="inlineStr">
@@ -40635,12 +40635,12 @@
       </c>
       <c r="AA317" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -40709,7 +40709,7 @@
         </is>
       </c>
       <c r="P318" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q318" t="inlineStr">
         <is>
@@ -40763,12 +40763,12 @@
       </c>
       <c r="AA318" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -40837,7 +40837,7 @@
         </is>
       </c>
       <c r="P319" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q319" t="inlineStr">
         <is>
@@ -40891,12 +40891,12 @@
       </c>
       <c r="AA319" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -40965,7 +40965,7 @@
         </is>
       </c>
       <c r="P320" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q320" t="inlineStr">
         <is>
@@ -41019,12 +41019,12 @@
       </c>
       <c r="AA320" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -41093,7 +41093,7 @@
         </is>
       </c>
       <c r="P321" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q321" t="inlineStr">
         <is>
@@ -41147,12 +41147,12 @@
       </c>
       <c r="AA321" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -41221,7 +41221,7 @@
         </is>
       </c>
       <c r="P322" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q322" t="inlineStr">
         <is>
@@ -41275,12 +41275,12 @@
       </c>
       <c r="AA322" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -41349,7 +41349,7 @@
         </is>
       </c>
       <c r="P323" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q323" t="inlineStr">
         <is>
@@ -41403,12 +41403,12 @@
       </c>
       <c r="AA323" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -41477,7 +41477,7 @@
         </is>
       </c>
       <c r="P324" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q324" t="inlineStr">
         <is>
@@ -41531,12 +41531,12 @@
       </c>
       <c r="AA324" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -41601,7 +41601,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P325" t="n">
@@ -41614,7 +41614,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S325" t="inlineStr">
@@ -41659,12 +41659,12 @@
       </c>
       <c r="AA325" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -41733,7 +41733,7 @@
         </is>
       </c>
       <c r="P326" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q326" t="inlineStr">
         <is>
@@ -41787,12 +41787,12 @@
       </c>
       <c r="AA326" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -41861,7 +41861,7 @@
         </is>
       </c>
       <c r="P327" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q327" t="inlineStr">
         <is>
@@ -41915,12 +41915,12 @@
       </c>
       <c r="AA327" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -41985,7 +41985,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P328" t="n">
@@ -41998,7 +41998,7 @@
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S328" t="inlineStr">
@@ -42043,12 +42043,12 @@
       </c>
       <c r="AA328" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -42117,7 +42117,7 @@
         </is>
       </c>
       <c r="P329" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q329" t="inlineStr">
         <is>
@@ -42171,12 +42171,12 @@
       </c>
       <c r="AA329" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB329" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -42245,7 +42245,7 @@
         </is>
       </c>
       <c r="P330" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q330" t="inlineStr">
         <is>
@@ -42299,12 +42299,12 @@
       </c>
       <c r="AA330" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -42327,7 +42327,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Mary Ann Boldin AKA Mary An Bouldin / Sharon M. Lott AKA Sharon M Gray AKA Sharon Lott Gray</t>
+          <t>Dora Mae Flowers AKA Doretta Mae Flowers / Viola Free Williams AKA Viola F Williams AKA Bonnie Free Williams</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -42369,7 +42369,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P331" t="n">
@@ -42382,7 +42382,7 @@
       </c>
       <c r="R331" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S331" t="inlineStr">
@@ -42427,12 +42427,12 @@
       </c>
       <c r="AA331" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -42501,7 +42501,7 @@
         </is>
       </c>
       <c r="P332" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q332" t="inlineStr">
         <is>
@@ -42555,12 +42555,12 @@
       </c>
       <c r="AA332" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -42629,7 +42629,7 @@
         </is>
       </c>
       <c r="P333" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q333" t="inlineStr">
         <is>
@@ -42683,12 +42683,12 @@
       </c>
       <c r="AA333" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -42757,7 +42757,7 @@
         </is>
       </c>
       <c r="P334" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q334" t="inlineStr">
         <is>
@@ -42811,12 +42811,12 @@
       </c>
       <c r="AA334" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -42885,7 +42885,7 @@
         </is>
       </c>
       <c r="P335" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q335" t="inlineStr">
         <is>
@@ -42939,12 +42939,12 @@
       </c>
       <c r="AA335" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -43009,7 +43009,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P336" t="inlineStr"/>
@@ -43026,7 +43026,7 @@
       </c>
       <c r="T336" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=23-CA-000671</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=23-CA-000671</t>
         </is>
       </c>
       <c r="U336" t="inlineStr">
@@ -43036,7 +43036,7 @@
       </c>
       <c r="V336" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W336" t="inlineStr">
@@ -43061,12 +43061,12 @@
       </c>
       <c r="AA336" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -43135,7 +43135,7 @@
         </is>
       </c>
       <c r="P337" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q337" t="inlineStr">
         <is>
@@ -43189,12 +43189,12 @@
       </c>
       <c r="AA337" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -43263,7 +43263,7 @@
         </is>
       </c>
       <c r="P338" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q338" t="inlineStr">
         <is>
@@ -43317,12 +43317,12 @@
       </c>
       <c r="AA338" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -43387,7 +43387,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P339" t="n">
@@ -43400,7 +43400,7 @@
       </c>
       <c r="R339" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S339" t="inlineStr">
@@ -43445,12 +43445,12 @@
       </c>
       <c r="AA339" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -43519,7 +43519,7 @@
         </is>
       </c>
       <c r="P340" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q340" t="inlineStr">
         <is>
@@ -43573,12 +43573,12 @@
       </c>
       <c r="AA340" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -43647,7 +43647,7 @@
         </is>
       </c>
       <c r="P341" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q341" t="inlineStr">
         <is>
@@ -43701,12 +43701,12 @@
       </c>
       <c r="AA341" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -43775,7 +43775,7 @@
         </is>
       </c>
       <c r="P342" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q342" t="inlineStr">
         <is>
@@ -43829,12 +43829,12 @@
       </c>
       <c r="AA342" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -43903,7 +43903,7 @@
         </is>
       </c>
       <c r="P343" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q343" t="inlineStr">
         <is>
@@ -43957,12 +43957,12 @@
       </c>
       <c r="AA343" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -44031,7 +44031,7 @@
         </is>
       </c>
       <c r="P344" t="n">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="Q344" t="inlineStr">
         <is>
@@ -44085,12 +44085,12 @@
       </c>
       <c r="AA344" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -44159,7 +44159,7 @@
         </is>
       </c>
       <c r="P345" t="n">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="Q345" t="inlineStr">
         <is>
@@ -44213,12 +44213,12 @@
       </c>
       <c r="AA345" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB345" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -44287,7 +44287,7 @@
         </is>
       </c>
       <c r="P346" t="n">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="Q346" t="inlineStr">
         <is>
@@ -44341,12 +44341,12 @@
       </c>
       <c r="AA346" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -44415,7 +44415,7 @@
         </is>
       </c>
       <c r="P347" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q347" t="inlineStr">
         <is>
@@ -44469,12 +44469,12 @@
       </c>
       <c r="AA347" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB347" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -44543,7 +44543,7 @@
         </is>
       </c>
       <c r="P348" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q348" t="inlineStr">
         <is>
@@ -44597,12 +44597,12 @@
       </c>
       <c r="AA348" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -44671,7 +44671,7 @@
         </is>
       </c>
       <c r="P349" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q349" t="inlineStr">
         <is>
@@ -44725,12 +44725,12 @@
       </c>
       <c r="AA349" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -44799,7 +44799,7 @@
         </is>
       </c>
       <c r="P350" t="n">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="Q350" t="inlineStr">
         <is>
@@ -44853,12 +44853,12 @@
       </c>
       <c r="AA350" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB350" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -44927,7 +44927,7 @@
         </is>
       </c>
       <c r="P351" t="n">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="Q351" t="inlineStr">
         <is>
@@ -44981,12 +44981,12 @@
       </c>
       <c r="AA351" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB351" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -45055,7 +45055,7 @@
         </is>
       </c>
       <c r="P352" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q352" t="inlineStr">
         <is>
@@ -45109,12 +45109,12 @@
       </c>
       <c r="AA352" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB352" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -45183,7 +45183,7 @@
         </is>
       </c>
       <c r="P353" t="n">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="Q353" t="inlineStr">
         <is>
@@ -45237,12 +45237,12 @@
       </c>
       <c r="AA353" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -45311,7 +45311,7 @@
         </is>
       </c>
       <c r="P354" t="n">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Q354" t="inlineStr">
         <is>
@@ -45365,12 +45365,12 @@
       </c>
       <c r="AA354" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -45435,7 +45435,7 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P355" t="inlineStr"/>
@@ -45452,7 +45452,7 @@
       </c>
       <c r="T355" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=22-CA-007538</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=22-CA-007538</t>
         </is>
       </c>
       <c r="U355" t="inlineStr">
@@ -45462,7 +45462,7 @@
       </c>
       <c r="V355" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W355" t="inlineStr">
@@ -45487,12 +45487,12 @@
       </c>
       <c r="AA355" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB355" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -45561,7 +45561,7 @@
         </is>
       </c>
       <c r="P356" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q356" t="inlineStr">
         <is>
@@ -45615,12 +45615,12 @@
       </c>
       <c r="AA356" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB356" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -45689,7 +45689,7 @@
         </is>
       </c>
       <c r="P357" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q357" t="inlineStr">
         <is>
@@ -45743,12 +45743,12 @@
       </c>
       <c r="AA357" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB357" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -45817,7 +45817,7 @@
         </is>
       </c>
       <c r="P358" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q358" t="inlineStr">
         <is>
@@ -45871,12 +45871,12 @@
       </c>
       <c r="AA358" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB358" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -45945,7 +45945,7 @@
         </is>
       </c>
       <c r="P359" t="n">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Q359" t="inlineStr">
         <is>
@@ -45999,12 +45999,12 @@
       </c>
       <c r="AA359" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -46069,7 +46069,7 @@
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P360" t="n">
@@ -46082,7 +46082,7 @@
       </c>
       <c r="R360" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S360" t="inlineStr">
@@ -46127,12 +46127,12 @@
       </c>
       <c r="AA360" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB360" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -46201,7 +46201,7 @@
         </is>
       </c>
       <c r="P361" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q361" t="inlineStr">
         <is>
@@ -46255,12 +46255,12 @@
       </c>
       <c r="AA361" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB361" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -46377,12 +46377,12 @@
       </c>
       <c r="AA362" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -46451,7 +46451,7 @@
         </is>
       </c>
       <c r="P363" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q363" t="inlineStr">
         <is>
@@ -46505,12 +46505,12 @@
       </c>
       <c r="AA363" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -46579,7 +46579,7 @@
         </is>
       </c>
       <c r="P364" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q364" t="inlineStr">
         <is>
@@ -46633,12 +46633,12 @@
       </c>
       <c r="AA364" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB364" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -46707,7 +46707,7 @@
         </is>
       </c>
       <c r="P365" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q365" t="inlineStr">
         <is>
@@ -46761,12 +46761,12 @@
       </c>
       <c r="AA365" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -46835,7 +46835,7 @@
         </is>
       </c>
       <c r="P366" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q366" t="inlineStr">
         <is>
@@ -46889,12 +46889,12 @@
       </c>
       <c r="AA366" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB366" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -46963,7 +46963,7 @@
         </is>
       </c>
       <c r="P367" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q367" t="inlineStr">
         <is>
@@ -47017,12 +47017,12 @@
       </c>
       <c r="AA367" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB367" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -47091,7 +47091,7 @@
         </is>
       </c>
       <c r="P368" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q368" t="inlineStr">
         <is>
@@ -47145,12 +47145,12 @@
       </c>
       <c r="AA368" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB368" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -47215,7 +47215,7 @@
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P369" t="inlineStr"/>
@@ -47232,7 +47232,7 @@
       </c>
       <c r="T369" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=25-CA-005347</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=25-CA-005347</t>
         </is>
       </c>
       <c r="U369" t="inlineStr">
@@ -47242,7 +47242,7 @@
       </c>
       <c r="V369" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W369" t="inlineStr">
@@ -47267,12 +47267,12 @@
       </c>
       <c r="AA369" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB369" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
